--- a/franquias/pwr_reports/KEYS Service Main Service Exceptions - Franquias (Stores)(2026-08-03 - 2026-08-09).xlsx
+++ b/franquias/pwr_reports/KEYS Service Main Service Exceptions - Franquias (Stores)(2026-08-03 - 2026-08-09).xlsx
@@ -908,51 +908,48 @@
     <t>187</t>
   </si>
   <si>
-    <t>155</t>
-  </si>
-  <si>
-    <t>R$ 41.956,98</t>
-  </si>
-  <si>
-    <t>431.5</t>
-  </si>
-  <si>
-    <t>261.2</t>
-  </si>
-  <si>
-    <t>5.71</t>
-  </si>
-  <si>
-    <t>19.7</t>
-  </si>
-  <si>
-    <t>7.3</t>
+    <t>121</t>
+  </si>
+  <si>
+    <t>R$ 42.334,49</t>
+  </si>
+  <si>
+    <t>448.4</t>
+  </si>
+  <si>
+    <t>273.9</t>
+  </si>
+  <si>
+    <t>5.76</t>
+  </si>
+  <si>
+    <t>19.8</t>
+  </si>
+  <si>
+    <t>7.4</t>
   </si>
   <si>
     <t>6.7</t>
   </si>
   <si>
-    <t>38.3%</t>
-  </si>
-  <si>
-    <t>19.2%</t>
+    <t>37.4%</t>
+  </si>
+  <si>
+    <t>19.1%</t>
   </si>
   <si>
     <t>2.2%</t>
   </si>
   <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>5.6%</t>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>5.5%</t>
   </si>
   <si>
     <t>1.3%</t>
   </si>
   <si>
-    <t>0.2%</t>
-  </si>
-  <si>
     <t>6.8%</t>
   </si>
   <si>
@@ -962,40 +959,40 @@
     <t>4.3%</t>
   </si>
   <si>
-    <t>10688.0</t>
-  </si>
-  <si>
-    <t>8683.0</t>
-  </si>
-  <si>
-    <t>976.0</t>
-  </si>
-  <si>
-    <t>113.0</t>
-  </si>
-  <si>
-    <t>2510.0</t>
-  </si>
-  <si>
-    <t>577.0</t>
-  </si>
-  <si>
-    <t>96.0</t>
-  </si>
-  <si>
-    <t>3088.0</t>
-  </si>
-  <si>
-    <t>1252.0</t>
-  </si>
-  <si>
-    <t>1944.0</t>
+    <t>11118.0</t>
+  </si>
+  <si>
+    <t>9056.0</t>
+  </si>
+  <si>
+    <t>1033.0</t>
+  </si>
+  <si>
+    <t>117.0</t>
+  </si>
+  <si>
+    <t>2590.0</t>
+  </si>
+  <si>
+    <t>598.0</t>
+  </si>
+  <si>
+    <t>99.0</t>
+  </si>
+  <si>
+    <t>3214.0</t>
+  </si>
+  <si>
+    <t>1312.0</t>
+  </si>
+  <si>
+    <t>2019.0</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>245.0</t>
+    <t>253.0</t>
   </si>
   <si>
     <t>1</t>
@@ -2246,7 +2243,7 @@
         <v>19521</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2277,7 +2274,7 @@
       </c>
       <c r="L6" s="4"/>
       <c r="M6" s="5">
-        <v>86064.42833333333</v>
+        <v>73769.509999999995</v>
       </c>
       <c r="N6" s="6">
         <v>743</v>
@@ -3758,7 +3755,7 @@
         <v>19546</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C16" s="4">
         <v>51</v>
@@ -3789,70 +3786,70 @@
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="5">
-        <v>43241.251666666671</v>
+        <v>45140.139999999999</v>
       </c>
       <c r="N16" s="6">
-        <v>406</v>
+        <v>493</v>
       </c>
       <c r="O16" s="6">
-        <v>222</v>
+        <v>267</v>
       </c>
       <c r="P16" s="7">
-        <v>3.8390573232323231</v>
+        <v>3.9391078838174276</v>
       </c>
       <c r="Q16" s="8">
-        <v>18.929109954751134</v>
+        <v>19.007268045112781</v>
       </c>
       <c r="R16" s="8">
-        <v>8.2676557077625574</v>
+        <v>8.2512624999999993</v>
       </c>
       <c r="S16" s="8">
         <v>7</v>
       </c>
       <c r="T16" s="9">
-        <v>0.34841628959276016</v>
+        <v>0.32330827067669171</v>
       </c>
       <c r="U16" s="9">
-        <v>0.16666666666666666</v>
+        <v>0.14606741573033707</v>
       </c>
       <c r="V16" s="9">
-        <v>0.018018018018018018</v>
+        <v>0.018726591760299626</v>
       </c>
       <c r="W16" s="9">
         <v>0</v>
       </c>
       <c r="X16" s="9">
-        <v>0.11261261261261261</v>
+        <v>0.10112359550561797</v>
       </c>
       <c r="Y16" s="9">
-        <v>0.0090090090090090089</v>
+        <v>0.0074906367041198503</v>
       </c>
       <c r="Z16" s="9">
         <v>0</v>
       </c>
       <c r="AA16" s="9">
-        <v>0.018018018018018018</v>
+        <v>0.018726591760299626</v>
       </c>
       <c r="AB16" s="9">
-        <v>0.0045045045045045045</v>
+        <v>0.0037453183520599251</v>
       </c>
       <c r="AC16" s="9">
-        <v>0.036036036036036036</v>
+        <v>0.029962546816479401</v>
       </c>
       <c r="AD16" s="6">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AE16" s="6">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AF16" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG16" s="6">
         <v>0</v>
       </c>
       <c r="AH16" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI16" s="6">
         <v>2</v>
@@ -3861,7 +3858,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL16" s="6">
         <v>1</v>
@@ -4072,7 +4069,7 @@
         <v>19550</v>
       </c>
       <c r="B18" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C18" s="4">
         <v>51</v>
@@ -4103,34 +4100,34 @@
       </c>
       <c r="L18" s="4"/>
       <c r="M18" s="5">
-        <v>36070.183333333334</v>
+        <v>38828.729999999996</v>
       </c>
       <c r="N18" s="6">
-        <v>290</v>
+        <v>367</v>
       </c>
       <c r="O18" s="6">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="P18" s="7">
-        <v>2.0526733788395903</v>
+        <v>2.1960359459459462</v>
       </c>
       <c r="Q18" s="8">
-        <v>10.819088888888889</v>
+        <v>11.664236805555555</v>
       </c>
       <c r="R18" s="8">
-        <v>1.8622504273504272</v>
+        <v>2.6280090277777775</v>
       </c>
       <c r="S18" s="8">
         <v>7</v>
       </c>
       <c r="T18" s="9">
-        <v>0.96581196581196582</v>
+        <v>0.92361111111111116</v>
       </c>
       <c r="U18" s="9">
-        <v>0.12820512820512819</v>
+        <v>0.125</v>
       </c>
       <c r="V18" s="9">
-        <v>0.059829059829059832</v>
+        <v>0.055555555555555552</v>
       </c>
       <c r="W18" s="9">
         <v>0</v>
@@ -4148,19 +4145,19 @@
         <v>0</v>
       </c>
       <c r="AB18" s="9">
-        <v>0.0085470085470085479</v>
+        <v>0.0069444444444444441</v>
       </c>
       <c r="AC18" s="9">
         <v>0</v>
       </c>
       <c r="AD18" s="6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AE18" s="6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AF18" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG18" s="6">
         <v>0</v>
@@ -4184,10 +4181,10 @@
         <v>0</v>
       </c>
       <c r="AN18" s="9">
-        <v>0.059829059829059832</v>
+        <v>0.0625</v>
       </c>
       <c r="AO18" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c t="s" r="AP18" s="4">
         <v>58</v>
@@ -4543,7 +4540,7 @@
         <v>19553</v>
       </c>
       <c r="B21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C21" s="4">
         <v>51</v>
@@ -4572,49 +4569,49 @@
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="5">
-        <v>52801.64166666667</v>
+        <v>59362</v>
       </c>
       <c r="N21" s="6">
-        <v>415</v>
+        <v>544</v>
       </c>
       <c r="O21" s="6">
-        <v>245</v>
+        <v>324</v>
       </c>
       <c r="P21" s="7">
-        <v>3.1500395238095238</v>
+        <v>3.3617270909090911</v>
       </c>
       <c r="Q21" s="8">
-        <v>16.72476244897959</v>
+        <v>16.952109567901235</v>
       </c>
       <c r="R21" s="8">
-        <v>6.5609049382716051</v>
+        <v>6.6585146417445493</v>
       </c>
       <c r="S21" s="8">
         <v>7</v>
       </c>
       <c r="T21" s="9">
-        <v>0.49795918367346936</v>
+        <v>0.45987654320987653</v>
       </c>
       <c r="U21" s="9">
-        <v>0.20408163265306123</v>
+        <v>0.19753086419753085</v>
       </c>
       <c r="V21" s="9">
-        <v>0.016326530612244899</v>
+        <v>0.027777777777777776</v>
       </c>
       <c r="W21" s="9">
-        <v>0.0081632653060000008</v>
+        <v>0.0092592592590000009</v>
       </c>
       <c r="X21" s="9">
-        <v>0.093877551020408165</v>
+        <v>0.07716049382716049</v>
       </c>
       <c r="Y21" s="9">
-        <v>0.0081632653061224497</v>
+        <v>0.0061728395061728392</v>
       </c>
       <c r="Z21" s="9">
-        <v>0.0040816326530612249</v>
+        <v>0.0030864197530864196</v>
       </c>
       <c r="AA21" s="9">
-        <v>0.0081632653061224497</v>
+        <v>0.012345679012345678</v>
       </c>
       <c r="AB21" s="9">
         <v>0</v>
@@ -4623,19 +4620,19 @@
         <v>0</v>
       </c>
       <c r="AD21" s="6">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="AE21" s="6">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="AF21" s="6">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AG21" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH21" s="6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI21" s="6">
         <v>2</v>
@@ -4644,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="AK21" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL21" s="6">
         <v>0</v>
@@ -4653,10 +4650,10 @@
         <v>0</v>
       </c>
       <c r="AN21" s="9">
-        <v>0.093877551020408165</v>
+        <v>0.086419753086419748</v>
       </c>
       <c r="AO21" s="6">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c t="s" r="AP21" s="4">
         <v>58</v>
@@ -5012,7 +5009,7 @@
         <v>19565</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -5043,61 +5040,61 @@
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="5">
-        <v>43031.076666666668</v>
+        <v>53742.440000000002</v>
       </c>
       <c r="N24" s="6">
-        <v>412</v>
+        <v>591</v>
       </c>
       <c r="O24" s="6">
-        <v>284</v>
+        <v>414</v>
       </c>
       <c r="P24" s="7">
-        <v>3.1002412048192776</v>
+        <v>3.3049581512605042</v>
       </c>
       <c r="Q24" s="8">
-        <v>16.465551760563379</v>
+        <v>18.035351089588378</v>
       </c>
       <c r="R24" s="8">
-        <v>6.2859212121212114</v>
+        <v>7.4891579081632651</v>
       </c>
       <c r="S24" s="8">
         <v>8</v>
       </c>
       <c r="T24" s="9">
-        <v>0.426056338028169</v>
+        <v>0.36803874092009686</v>
       </c>
       <c r="U24" s="9">
-        <v>0.25</v>
+        <v>0.20289855072463769</v>
       </c>
       <c r="V24" s="9">
-        <v>0.02464788732394366</v>
+        <v>0.016908212560386472</v>
       </c>
       <c r="W24" s="9">
         <v>0</v>
       </c>
       <c r="X24" s="9">
-        <v>0.12323943661971831</v>
+        <v>0.089371980676328497</v>
       </c>
       <c r="Y24" s="9">
-        <v>0.031690140845070422</v>
+        <v>0.021739130434782608</v>
       </c>
       <c r="Z24" s="9">
         <v>0</v>
       </c>
       <c r="AA24" s="9">
-        <v>0.11619718309859155</v>
+        <v>0.089371980676328497</v>
       </c>
       <c r="AB24" s="9">
-        <v>0.052816901408450703</v>
+        <v>0.043478260869565216</v>
       </c>
       <c r="AC24" s="9">
-        <v>0</v>
+        <v>0.0096618357487922701</v>
       </c>
       <c r="AD24" s="6">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="AE24" s="6">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="AF24" s="6">
         <v>7</v>
@@ -5106,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="AH24" s="6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AI24" s="6">
         <v>9</v>
@@ -5115,13 +5112,13 @@
         <v>0</v>
       </c>
       <c r="AK24" s="6">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="AL24" s="6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AM24" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN24" s="9">
         <v>0</v>
@@ -6111,7 +6108,7 @@
         <v>19596</v>
       </c>
       <c r="B31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C31" s="4">
         <v>51</v>
@@ -6140,70 +6137,70 @@
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="5">
-        <v>44391.561666666668</v>
+        <v>48944.869999999995</v>
       </c>
       <c r="N31" s="6">
-        <v>428</v>
+        <v>537</v>
       </c>
       <c r="O31" s="6">
-        <v>229</v>
+        <v>287</v>
       </c>
       <c r="P31" s="7">
-        <v>3.3007228915662647</v>
+        <v>3.271647509578544</v>
       </c>
       <c r="Q31" s="8">
-        <v>18.93845043859649</v>
+        <v>18.233742807017542</v>
       </c>
       <c r="R31" s="8">
-        <v>9.0296375565610862</v>
+        <v>8.3274575539568332</v>
       </c>
       <c r="S31" s="8">
         <v>7</v>
       </c>
       <c r="T31" s="9">
-        <v>0.35526315789473684</v>
+        <v>0.39649122807017545</v>
       </c>
       <c r="U31" s="9">
-        <v>0.20960698689956331</v>
+        <v>0.20905923344947736</v>
       </c>
       <c r="V31" s="9">
-        <v>0.048034934497816595</v>
+        <v>0.041811846689895474</v>
       </c>
       <c r="W31" s="9">
         <v>0</v>
       </c>
       <c r="X31" s="9">
-        <v>0.09606986899563319</v>
+        <v>0.10104529616724739</v>
       </c>
       <c r="Y31" s="9">
-        <v>0.026200873362445413</v>
+        <v>0.020905923344947737</v>
       </c>
       <c r="Z31" s="9">
         <v>0</v>
       </c>
       <c r="AA31" s="9">
-        <v>0.030567685589519649</v>
+        <v>0.024390243902439025</v>
       </c>
       <c r="AB31" s="9">
-        <v>0.056768558951965066</v>
+        <v>0.059233449477351915</v>
       </c>
       <c r="AC31" s="9">
-        <v>0.017467248908296942</v>
+        <v>0.013937282229965157</v>
       </c>
       <c r="AD31" s="6">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="AE31" s="6">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AF31" s="6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG31" s="6">
         <v>0</v>
       </c>
       <c r="AH31" s="6">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AI31" s="6">
         <v>6</v>
@@ -6215,7 +6212,7 @@
         <v>7</v>
       </c>
       <c r="AL31" s="6">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AM31" s="6">
         <v>4</v>
@@ -6733,7 +6730,7 @@
         <v>19601</v>
       </c>
       <c r="B35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C35" s="4">
         <v>51</v>
@@ -6764,61 +6761,61 @@
       </c>
       <c r="L35" s="4"/>
       <c r="M35" s="5">
-        <v>43097.611666666664</v>
+        <v>51976.509999999995</v>
       </c>
       <c r="N35" s="6">
-        <v>419</v>
+        <v>577</v>
       </c>
       <c r="O35" s="6">
-        <v>246</v>
+        <v>328</v>
       </c>
       <c r="P35" s="7">
-        <v>2.6629020304568525</v>
+        <v>3.0301459016393442</v>
       </c>
       <c r="Q35" s="8">
-        <v>16.405758943089431</v>
+        <v>17.175864024390243</v>
       </c>
       <c r="R35" s="8">
-        <v>6.0520306722689075</v>
+        <v>6.5262053459119489</v>
       </c>
       <c r="S35" s="8">
         <v>8</v>
       </c>
       <c r="T35" s="9">
-        <v>0.5</v>
+        <v>0.43292682926829268</v>
       </c>
       <c r="U35" s="9">
-        <v>0.22357723577235772</v>
+        <v>0.2347560975609756</v>
       </c>
       <c r="V35" s="9">
-        <v>0.02032520325203252</v>
+        <v>0.01524390243902439</v>
       </c>
       <c r="W35" s="9">
         <v>0</v>
       </c>
       <c r="X35" s="9">
-        <v>0.06097560975609756</v>
+        <v>0.051829268292682924</v>
       </c>
       <c r="Y35" s="9">
-        <v>0.0040650406504065045</v>
+        <v>0.0060975609756097563</v>
       </c>
       <c r="Z35" s="9">
         <v>0</v>
       </c>
       <c r="AA35" s="9">
-        <v>0.06910569105691057</v>
+        <v>0.057926829268292686</v>
       </c>
       <c r="AB35" s="9">
-        <v>0.056910569105691054</v>
+        <v>0.10365853658536585</v>
       </c>
       <c r="AC35" s="9">
-        <v>0.032520325203252036</v>
+        <v>0.024390243902439025</v>
       </c>
       <c r="AD35" s="6">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="AE35" s="6">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="AF35" s="6">
         <v>5</v>
@@ -6827,19 +6824,19 @@
         <v>0</v>
       </c>
       <c r="AH35" s="6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI35" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ35" s="6">
         <v>0</v>
       </c>
       <c r="AK35" s="6">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AL35" s="6">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="AM35" s="6">
         <v>8</v>
@@ -7181,7 +7178,7 @@
         <v>422</v>
       </c>
       <c r="O38" s="6">
-        <v>66</v>
+        <v>247</v>
       </c>
       <c r="P38" s="7">
         <v>3.7685453237410074</v>
@@ -7199,16 +7196,16 @@
         <v>0.63157894736842102</v>
       </c>
       <c r="U38" s="9">
-        <v>0.030303030303030304</v>
+        <v>0.032388663967611336</v>
       </c>
       <c r="V38" s="9">
-        <v>0.015151515151515152</v>
+        <v>0.0080971659919028341</v>
       </c>
       <c r="W38" s="9">
         <v>0</v>
       </c>
       <c r="X38" s="9">
-        <v>0.015151515151515152</v>
+        <v>0.012145748987854251</v>
       </c>
       <c r="Y38" s="9">
         <v>0</v>
@@ -7217,43 +7214,43 @@
         <v>0</v>
       </c>
       <c r="AA38" s="9">
-        <v>0</v>
+        <v>0.004048582995951417</v>
       </c>
       <c r="AB38" s="9">
         <v>0</v>
       </c>
       <c r="AC38" s="9">
-        <v>0</v>
+        <v>0.0080971659919028341</v>
       </c>
       <c r="AD38" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE38" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF38" s="6">
         <v>2</v>
       </c>
-      <c r="AE38" s="6">
+      <c r="AG38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK38" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL38" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM38" s="6">
         <v>2</v>
-      </c>
-      <c r="AF38" s="6">
-        <v>1</v>
-      </c>
-      <c r="AG38" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI38" s="6">
-        <v>0</v>
-      </c>
-      <c r="AJ38" s="6">
-        <v>0</v>
-      </c>
-      <c r="AK38" s="6">
-        <v>0</v>
-      </c>
-      <c r="AL38" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM38" s="6">
-        <v>0</v>
       </c>
       <c r="AN38" s="9">
         <v>0</v>
@@ -7458,7 +7455,7 @@
         <v>19615</v>
       </c>
       <c r="B40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C40" s="4">
         <v>51</v>
@@ -7489,70 +7486,70 @@
       </c>
       <c r="L40" s="4"/>
       <c r="M40" s="5">
-        <v>41471.33666666667</v>
+        <v>45697.510000000002</v>
       </c>
       <c r="N40" s="6">
-        <v>420</v>
+        <v>551</v>
       </c>
       <c r="O40" s="6">
-        <v>333</v>
+        <v>446</v>
       </c>
       <c r="P40" s="7">
-        <v>2.8418979166666669</v>
+        <v>2.9595780316344467</v>
       </c>
       <c r="Q40" s="8">
-        <v>19.208536585365852</v>
+        <v>22.123787528868363</v>
       </c>
       <c r="R40" s="8">
-        <v>10.135905787781351</v>
+        <v>12.909495192307693</v>
       </c>
       <c r="S40" s="8">
         <v>7</v>
       </c>
       <c r="T40" s="9">
-        <v>0.34756097560975607</v>
+        <v>0.28406466512702078</v>
       </c>
       <c r="U40" s="9">
-        <v>0.23123123123123124</v>
+        <v>0.23542600896860988</v>
       </c>
       <c r="V40" s="9">
-        <v>0.012012012012012012</v>
+        <v>0.011210762331838564</v>
       </c>
       <c r="W40" s="9">
         <v>0</v>
       </c>
       <c r="X40" s="9">
-        <v>0.1111111111111111</v>
+        <v>0.09641255605381166</v>
       </c>
       <c r="Y40" s="9">
-        <v>0.0090090090090090089</v>
+        <v>0.0067264573991031393</v>
       </c>
       <c r="Z40" s="9">
         <v>0</v>
       </c>
       <c r="AA40" s="9">
-        <v>0.06006006006006006</v>
+        <v>0.049327354260089683</v>
       </c>
       <c r="AB40" s="9">
-        <v>0.0090090090090090089</v>
+        <v>0.0067264573991031393</v>
       </c>
       <c r="AC40" s="9">
-        <v>0.066066066066066062</v>
+        <v>0.091928251121076235</v>
       </c>
       <c r="AD40" s="6">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="AE40" s="6">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="AF40" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG40" s="6">
         <v>0</v>
       </c>
       <c r="AH40" s="6">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="AI40" s="6">
         <v>3</v>
@@ -7561,13 +7558,13 @@
         <v>0</v>
       </c>
       <c r="AK40" s="6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL40" s="6">
         <v>3</v>
       </c>
       <c r="AM40" s="6">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="AN40" s="9">
         <v>0</v>
@@ -7650,7 +7647,7 @@
         <v>668</v>
       </c>
       <c r="O41" s="6">
-        <v>319</v>
+        <v>402</v>
       </c>
       <c r="P41" s="7">
         <v>9.9941057926829266</v>
@@ -7668,64 +7665,64 @@
         <v>0.30597014925373134</v>
       </c>
       <c r="U41" s="9">
-        <v>0.13479623824451412</v>
+        <v>0.14676616915422885</v>
       </c>
       <c r="V41" s="9">
-        <v>0.003134796238244514</v>
+        <v>0.0049751243781094526</v>
       </c>
       <c r="W41" s="9">
         <v>0</v>
       </c>
       <c r="X41" s="9">
-        <v>0.028213166144200628</v>
+        <v>0.02736318407960199</v>
       </c>
       <c r="Y41" s="9">
-        <v>0</v>
+        <v>0.0024875621890547263</v>
       </c>
       <c r="Z41" s="9">
-        <v>0.003134796238244514</v>
+        <v>0.0024875621890547263</v>
       </c>
       <c r="AA41" s="9">
-        <v>0.072100313479623826</v>
+        <v>0.092039800995024873</v>
       </c>
       <c r="AB41" s="9">
-        <v>0.025078369905956112</v>
+        <v>0.022388059701492536</v>
       </c>
       <c r="AC41" s="9">
-        <v>0.006269592476489028</v>
+        <v>0.0049751243781094526</v>
       </c>
       <c r="AD41" s="6">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="AE41" s="6">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="AF41" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG41" s="6">
         <v>0</v>
       </c>
       <c r="AH41" s="6">
+        <v>11</v>
+      </c>
+      <c r="AI41" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ41" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK41" s="6">
+        <v>37</v>
+      </c>
+      <c r="AL41" s="6">
         <v>9</v>
-      </c>
-      <c r="AI41" s="6">
-        <v>0</v>
-      </c>
-      <c r="AJ41" s="6">
-        <v>1</v>
-      </c>
-      <c r="AK41" s="6">
-        <v>23</v>
-      </c>
-      <c r="AL41" s="6">
-        <v>8</v>
       </c>
       <c r="AM41" s="6">
         <v>2</v>
       </c>
       <c r="AN41" s="9">
-        <v>0.0094043887147335428</v>
+        <v>0.007462686567164179</v>
       </c>
       <c r="AO41" s="6">
         <v>3</v>
@@ -8340,7 +8337,7 @@
         <v>19624</v>
       </c>
       <c r="B46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C46" s="4">
         <v>51</v>
@@ -8369,70 +8366,70 @@
       </c>
       <c r="L46" s="4"/>
       <c r="M46" s="5">
-        <v>23033.359999999997</v>
+        <v>28066.539999999997</v>
       </c>
       <c r="N46" s="6">
-        <v>237</v>
+        <v>331</v>
       </c>
       <c r="O46" s="6">
-        <v>110</v>
+        <v>157</v>
       </c>
       <c r="P46" s="7">
-        <v>2.5236170212765954</v>
+        <v>2.6206948640483385</v>
       </c>
       <c r="Q46" s="8">
-        <v>13.954091818181819</v>
+        <v>14.670807643312102</v>
       </c>
       <c r="R46" s="8">
-        <v>5.3781660000000002</v>
+        <v>5.8083328767123295</v>
       </c>
       <c r="S46" s="8">
         <v>7</v>
       </c>
       <c r="T46" s="9">
-        <v>0.67272727272727273</v>
+        <v>0.61146496815286622</v>
       </c>
       <c r="U46" s="9">
-        <v>0.25454545454545452</v>
+        <v>0.20382165605095542</v>
       </c>
       <c r="V46" s="9">
-        <v>0.018181818181818181</v>
+        <v>0.019108280254777069</v>
       </c>
       <c r="W46" s="9">
-        <v>0.00909090909</v>
+        <v>0.0063694267510000001</v>
       </c>
       <c r="X46" s="9">
-        <v>0.10000000000000001</v>
+        <v>0.082802547770700632</v>
       </c>
       <c r="Y46" s="9">
-        <v>0.054545454545454543</v>
+        <v>0.038216560509554139</v>
       </c>
       <c r="Z46" s="9">
-        <v>0.0090909090909090905</v>
+        <v>0.006369426751592357</v>
       </c>
       <c r="AA46" s="9">
-        <v>0.14545454545454545</v>
+        <v>0.10828025477707007</v>
       </c>
       <c r="AB46" s="9">
-        <v>0.018181818181818181</v>
+        <v>0.012738853503184714</v>
       </c>
       <c r="AC46" s="9">
-        <v>0.018181818181818181</v>
+        <v>0.012738853503184714</v>
       </c>
       <c r="AD46" s="6">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AE46" s="6">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AF46" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG46" s="6">
         <v>1</v>
       </c>
       <c r="AH46" s="6">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AI46" s="6">
         <v>6</v>
@@ -8441,7 +8438,7 @@
         <v>1</v>
       </c>
       <c r="AK46" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL46" s="6">
         <v>2</v>
@@ -9375,7 +9372,7 @@
         <v>19647</v>
       </c>
       <c r="B53" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C53" s="4">
         <v>51</v>
@@ -9404,40 +9401,40 @@
       </c>
       <c r="L53" s="4"/>
       <c r="M53" s="5">
-        <v>29951.460000000003</v>
+        <v>33502.190000000002</v>
       </c>
       <c r="N53" s="6">
-        <v>268</v>
+        <v>350</v>
       </c>
       <c r="O53" s="6">
-        <v>190</v>
+        <v>238</v>
       </c>
       <c r="P53" s="7">
-        <v>4.6347377289377292</v>
+        <v>6.7962293296089387</v>
       </c>
       <c r="Q53" s="8">
-        <v>21.511403157894737</v>
+        <v>24.087534873949579</v>
       </c>
       <c r="R53" s="8">
-        <v>8.8296494736842099</v>
+        <v>9.9695382352941184</v>
       </c>
       <c r="S53" s="8">
         <v>8</v>
       </c>
       <c r="T53" s="9">
-        <v>0.27368421052631581</v>
+        <v>0.22268907563025211</v>
       </c>
       <c r="U53" s="9">
-        <v>0.073684210526315783</v>
+        <v>0.067226890756302518</v>
       </c>
       <c r="V53" s="9">
-        <v>0</v>
+        <v>0.0042016806722689074</v>
       </c>
       <c r="W53" s="9">
-        <v>0.005263157894</v>
+        <v>0.0042016806720000001</v>
       </c>
       <c r="X53" s="9">
-        <v>0.042105263157894736</v>
+        <v>0.033613445378151259</v>
       </c>
       <c r="Y53" s="9">
         <v>0</v>
@@ -9446,22 +9443,22 @@
         <v>0</v>
       </c>
       <c r="AA53" s="9">
-        <v>0.005263157894736842</v>
+        <v>0.0084033613445378148</v>
       </c>
       <c r="AB53" s="9">
-        <v>0.026315789473684209</v>
+        <v>0.02100840336134454</v>
       </c>
       <c r="AC53" s="9">
         <v>0</v>
       </c>
       <c r="AD53" s="6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AE53" s="6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AF53" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG53" s="6">
         <v>1</v>
@@ -9476,7 +9473,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL53" s="6">
         <v>5</v>
@@ -9530,7 +9527,7 @@
         <v>19648</v>
       </c>
       <c r="B54" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C54" s="4">
         <v>51</v>
@@ -9561,79 +9558,79 @@
       </c>
       <c r="L54" s="4"/>
       <c r="M54" s="5">
-        <v>33276.949999999997</v>
+        <v>38383.399999999987</v>
       </c>
       <c r="N54" s="6">
-        <v>324</v>
+        <v>429</v>
       </c>
       <c r="O54" s="6">
-        <v>178</v>
+        <v>241</v>
       </c>
       <c r="P54" s="7">
-        <v>6.2680731249999999</v>
+        <v>5.9278040000000001</v>
       </c>
       <c r="Q54" s="8">
-        <v>19.673969662921351</v>
+        <v>21.347441078838173</v>
       </c>
       <c r="R54" s="8">
-        <v>6.2542387283237</v>
+        <v>8.2714893617021268</v>
       </c>
       <c r="S54" s="8">
         <v>7</v>
       </c>
       <c r="T54" s="9">
-        <v>0.33146067415730335</v>
+        <v>0.29045643153526973</v>
       </c>
       <c r="U54" s="9">
-        <v>0.12921348314606743</v>
+        <v>0.12448132780082988</v>
       </c>
       <c r="V54" s="9">
-        <v>0.033707865168539325</v>
+        <v>0.037344398340248962</v>
       </c>
       <c r="W54" s="9">
         <v>0</v>
       </c>
       <c r="X54" s="9">
-        <v>0.056179775280898875</v>
+        <v>0.062240663900414939</v>
       </c>
       <c r="Y54" s="9">
-        <v>0.011235955056179775</v>
+        <v>0.012448132780082987</v>
       </c>
       <c r="Z54" s="9">
         <v>0</v>
       </c>
       <c r="AA54" s="9">
-        <v>0.0449438202247191</v>
+        <v>0.037344398340248962</v>
       </c>
       <c r="AB54" s="9">
-        <v>0.02247191011235955</v>
+        <v>0.016597510373443983</v>
       </c>
       <c r="AC54" s="9">
         <v>0</v>
       </c>
       <c r="AD54" s="6">
+        <v>40</v>
+      </c>
+      <c r="AE54" s="6">
         <v>30</v>
       </c>
-      <c r="AE54" s="6">
-        <v>23</v>
-      </c>
       <c r="AF54" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AG54" s="6">
         <v>0</v>
       </c>
       <c r="AH54" s="6">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AI54" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ54" s="6">
         <v>0</v>
       </c>
       <c r="AK54" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL54" s="6">
         <v>4</v>
@@ -9687,7 +9684,7 @@
         <v>19649</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>51</v>
@@ -9716,82 +9713,82 @@
       </c>
       <c r="L55" s="4"/>
       <c r="M55" s="5">
-        <v>48284.459999999999</v>
+        <v>55698.099999999999</v>
       </c>
       <c r="N55" s="6">
-        <v>458</v>
+        <v>624</v>
       </c>
       <c r="O55" s="6">
-        <v>187</v>
+        <v>260</v>
       </c>
       <c r="P55" s="7">
-        <v>2.2450452702702703</v>
+        <v>3.2038294214876033</v>
       </c>
       <c r="Q55" s="8">
-        <v>17.078877005347593</v>
+        <v>17.771153846153847</v>
       </c>
       <c r="R55" s="8">
-        <v>7.2728364640883978</v>
+        <v>7.2039844621513947</v>
       </c>
       <c r="S55" s="8">
         <v>8</v>
       </c>
       <c r="T55" s="9">
-        <v>0.47593582887700536</v>
+        <v>0.44615384615384618</v>
       </c>
       <c r="U55" s="9">
-        <v>0.32085561497326204</v>
+        <v>0.27692307692307694</v>
       </c>
       <c r="V55" s="9">
-        <v>0.021390374331550801</v>
+        <v>0.023076923076923078</v>
       </c>
       <c r="W55" s="9">
-        <v>0.010695187165</v>
+        <v>0.0076923076919999996</v>
       </c>
       <c r="X55" s="9">
-        <v>0.23529411764705882</v>
+        <v>0.20000000000000001</v>
       </c>
       <c r="Y55" s="9">
-        <v>0.021390374331550801</v>
+        <v>0.023076923076923078</v>
       </c>
       <c r="Z55" s="9">
         <v>0</v>
       </c>
       <c r="AA55" s="9">
-        <v>0.058823529411764705</v>
+        <v>0.057692307692307696</v>
       </c>
       <c r="AB55" s="9">
-        <v>0.048128342245989303</v>
+        <v>0.038461538461538464</v>
       </c>
       <c r="AC55" s="9">
         <v>0</v>
       </c>
       <c r="AD55" s="6">
+        <v>89</v>
+      </c>
+      <c r="AE55" s="6">
         <v>72</v>
       </c>
-      <c r="AE55" s="6">
-        <v>60</v>
-      </c>
       <c r="AF55" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG55" s="6">
         <v>2</v>
       </c>
       <c r="AH55" s="6">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="AI55" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AJ55" s="6">
         <v>0</v>
       </c>
       <c r="AK55" s="6">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AL55" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM55" s="6">
         <v>0</v>
@@ -9997,7 +9994,7 @@
         <v>19654</v>
       </c>
       <c r="B57" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c t="s" r="C57" s="4">
         <v>51</v>
@@ -10026,82 +10023,82 @@
       </c>
       <c r="L57" s="4"/>
       <c r="M57" s="5">
-        <v>29293.781999999996</v>
+        <v>38354.859999999993</v>
       </c>
       <c r="N57" s="6">
-        <v>252</v>
+        <v>462</v>
       </c>
       <c r="O57" s="6">
-        <v>108</v>
+        <v>210</v>
       </c>
       <c r="P57" s="7">
-        <v>3.5140004</v>
+        <v>3.6241687361419066</v>
       </c>
       <c r="Q57" s="8">
-        <v>15.308795370370369</v>
+        <v>16.126983809523811</v>
       </c>
       <c r="R57" s="8">
-        <v>5.2138895833333327</v>
+        <v>5.4694876923076921</v>
       </c>
       <c r="S57" s="8">
         <v>8</v>
       </c>
       <c r="T57" s="9">
-        <v>0.53703703703703709</v>
+        <v>0.48095238095238096</v>
       </c>
       <c r="U57" s="9">
-        <v>0.27777777777777779</v>
+        <v>0.20952380952380953</v>
       </c>
       <c r="V57" s="9">
-        <v>0.018518518518518517</v>
+        <v>0.014285714285714285</v>
       </c>
       <c r="W57" s="9">
         <v>0</v>
       </c>
       <c r="X57" s="9">
-        <v>0.15740740740740741</v>
+        <v>0.10476190476190476</v>
       </c>
       <c r="Y57" s="9">
-        <v>0.07407407407407407</v>
+        <v>0.047619047619047616</v>
       </c>
       <c r="Z57" s="9">
         <v>0</v>
       </c>
       <c r="AA57" s="9">
-        <v>0.1388888888888889</v>
+        <v>0.10952380952380952</v>
       </c>
       <c r="AB57" s="9">
-        <v>0.064814814814814811</v>
+        <v>0.047619047619047616</v>
       </c>
       <c r="AC57" s="9">
         <v>0</v>
       </c>
       <c r="AD57" s="6">
-        <v>49</v>
+        <v>68</v>
       </c>
       <c r="AE57" s="6">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="AF57" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG57" s="6">
         <v>0</v>
       </c>
       <c r="AH57" s="6">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AI57" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AJ57" s="6">
         <v>0</v>
       </c>
       <c r="AK57" s="6">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AL57" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AM57" s="6">
         <v>0</v>
@@ -10249,7 +10246,7 @@
         <v>19657</v>
       </c>
       <c r="B59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C59" s="4">
         <v>51</v>
@@ -10280,82 +10277,82 @@
       </c>
       <c r="L59" s="4"/>
       <c r="M59" s="5">
-        <v>34192.981666666667</v>
+        <v>37571.270000000004</v>
       </c>
       <c r="N59" s="6">
-        <v>306</v>
+        <v>390</v>
       </c>
       <c r="O59" s="6">
-        <v>157</v>
+        <v>205</v>
       </c>
       <c r="P59" s="7">
-        <v>5.791216216216216</v>
+        <v>6.1220316622691291</v>
       </c>
       <c r="Q59" s="8">
-        <v>18.452992307692309</v>
+        <v>19.215686764705882</v>
       </c>
       <c r="R59" s="8">
-        <v>5.8300006451612898</v>
+        <v>6.2451326732673271</v>
       </c>
       <c r="S59" s="8">
         <v>7</v>
       </c>
       <c r="T59" s="9">
-        <v>0.23076923076923078</v>
+        <v>0.19607843137254902</v>
       </c>
       <c r="U59" s="9">
-        <v>0.24203821656050956</v>
+        <v>0.23414634146341465</v>
       </c>
       <c r="V59" s="9">
-        <v>0.031847133757961783</v>
+        <v>0.024390243902439025</v>
       </c>
       <c r="W59" s="9">
-        <v>0</v>
+        <v>0.0048780487799999998</v>
       </c>
       <c r="X59" s="9">
-        <v>0.019108280254777069</v>
+        <v>0.014634146341463415</v>
       </c>
       <c r="Y59" s="9">
-        <v>0</v>
+        <v>0.0048780487804878049</v>
       </c>
       <c r="Z59" s="9">
-        <v>0.006369426751592357</v>
+        <v>0.0097560975609756097</v>
       </c>
       <c r="AA59" s="9">
-        <v>0.006369426751592357</v>
+        <v>0.0097560975609756097</v>
       </c>
       <c r="AB59" s="9">
-        <v>0.16560509554140126</v>
+        <v>0.16585365853658537</v>
       </c>
       <c r="AC59" s="9">
-        <v>0.038216560509554139</v>
+        <v>0.029268292682926831</v>
       </c>
       <c r="AD59" s="6">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="AE59" s="6">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AF59" s="6">
         <v>5</v>
       </c>
       <c r="AG59" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH59" s="6">
         <v>3</v>
       </c>
       <c r="AI59" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ59" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK59" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL59" s="6">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AM59" s="6">
         <v>6</v>
@@ -10620,7 +10617,7 @@
         <v>0.0052493438320209973</v>
       </c>
       <c r="W61" s="9">
-        <v>0</v>
+        <v>0.0026246719160000001</v>
       </c>
       <c r="X61" s="9">
         <v>0.020997375328083989</v>
@@ -10650,7 +10647,7 @@
         <v>2</v>
       </c>
       <c r="AG61" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH61" s="6">
         <v>8</v>
@@ -11441,7 +11438,7 @@
         <v>19685</v>
       </c>
       <c r="B67" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C67" s="4">
         <v>51</v>
@@ -11472,64 +11469,64 @@
       </c>
       <c r="L67" s="4"/>
       <c r="M67" s="5">
-        <v>25134.246666666662</v>
+        <v>26353.790000000001</v>
       </c>
       <c r="N67" s="6">
-        <v>241</v>
+        <v>292</v>
       </c>
       <c r="O67" s="6">
-        <v>188</v>
+        <v>216</v>
       </c>
       <c r="P67" s="7">
-        <v>7.1342138211382107</v>
+        <v>7.3023645270270263</v>
       </c>
       <c r="Q67" s="8">
-        <v>19.864349197860964</v>
+        <v>22.114495813953489</v>
       </c>
       <c r="R67" s="8">
-        <v>7.545269032258064</v>
+        <v>10.00288659217877</v>
       </c>
       <c r="S67" s="8">
         <v>7</v>
       </c>
       <c r="T67" s="9">
-        <v>0.30481283422459893</v>
+        <v>0.27906976744186046</v>
       </c>
       <c r="U67" s="9">
-        <v>0.28723404255319152</v>
+        <v>0.31018518518518517</v>
       </c>
       <c r="V67" s="9">
-        <v>0.0053191489361702126</v>
+        <v>0.0092592592592592587</v>
       </c>
       <c r="W67" s="9">
         <v>0</v>
       </c>
       <c r="X67" s="9">
-        <v>0.026595744680851064</v>
+        <v>0.023148148148148147</v>
       </c>
       <c r="Y67" s="9">
-        <v>0.0053191489361702126</v>
+        <v>0.0046296296296296294</v>
       </c>
       <c r="Z67" s="9">
-        <v>0.0053191489361702126</v>
+        <v>0.0046296296296296294</v>
       </c>
       <c r="AA67" s="9">
-        <v>0.25531914893617019</v>
+        <v>0.24537037037037038</v>
       </c>
       <c r="AB67" s="9">
         <v>0</v>
       </c>
       <c r="AC67" s="9">
-        <v>0</v>
+        <v>0.046296296296296294</v>
       </c>
       <c r="AD67" s="6">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="AE67" s="6">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="AF67" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG67" s="6">
         <v>0</v>
@@ -11544,13 +11541,13 @@
         <v>1</v>
       </c>
       <c r="AK67" s="6">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="AL67" s="6">
         <v>0</v>
       </c>
       <c r="AM67" s="6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AN67" s="9">
         <v>0</v>
@@ -11598,7 +11595,7 @@
         <v>19687</v>
       </c>
       <c r="B68" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C68" s="4">
         <v>51</v>
@@ -11629,40 +11626,40 @@
       </c>
       <c r="L68" s="4"/>
       <c r="M68" s="5">
-        <v>34525.411666666667</v>
+        <v>34514.839999999997</v>
       </c>
       <c r="N68" s="6">
-        <v>379</v>
+        <v>446</v>
       </c>
       <c r="O68" s="6">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="P68" s="7">
-        <v>6.1386885885885887</v>
+        <v>6.1113966580976857</v>
       </c>
       <c r="Q68" s="8">
-        <v>22.46709487179487</v>
+        <v>20.849668000000001</v>
       </c>
       <c r="R68" s="8">
-        <v>11.38225806451613</v>
+        <v>10.090171794871795</v>
       </c>
       <c r="S68" s="8">
         <v>7</v>
       </c>
       <c r="T68" s="9">
-        <v>0.38461538461538464</v>
+        <v>0.41999999999999998</v>
       </c>
       <c r="U68" s="9">
-        <v>0.38461538461538464</v>
+        <v>0.44</v>
       </c>
       <c r="V68" s="9">
-        <v>0.076923076923076927</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="W68" s="9">
         <v>0</v>
       </c>
       <c r="X68" s="9">
-        <v>0.05128205128205128</v>
+        <v>0.059999999999999998</v>
       </c>
       <c r="Y68" s="9">
         <v>0</v>
@@ -11671,40 +11668,40 @@
         <v>0</v>
       </c>
       <c r="AA68" s="9">
-        <v>0.33333333333333331</v>
+        <v>0.35999999999999999</v>
       </c>
       <c r="AB68" s="9">
-        <v>0</v>
+        <v>0.040000000000000001</v>
       </c>
       <c r="AC68" s="9">
         <v>0</v>
       </c>
       <c r="AD68" s="6">
+        <v>28</v>
+      </c>
+      <c r="AE68" s="6">
+        <v>22</v>
+      </c>
+      <c r="AF68" s="6">
+        <v>5</v>
+      </c>
+      <c r="AG68" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI68" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ68" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="6">
         <v>18</v>
       </c>
-      <c r="AE68" s="6">
-        <v>15</v>
-      </c>
-      <c r="AF68" s="6">
-        <v>3</v>
-      </c>
-      <c r="AG68" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH68" s="6">
+      <c r="AL68" s="6">
         <v>2</v>
-      </c>
-      <c r="AI68" s="6">
-        <v>0</v>
-      </c>
-      <c r="AJ68" s="6">
-        <v>0</v>
-      </c>
-      <c r="AK68" s="6">
-        <v>13</v>
-      </c>
-      <c r="AL68" s="6">
-        <v>0</v>
       </c>
       <c r="AM68" s="6">
         <v>0</v>
@@ -11912,7 +11909,7 @@
         <v>19689</v>
       </c>
       <c r="B70" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C70" s="4">
         <v>51</v>
@@ -11943,61 +11940,61 @@
       </c>
       <c r="L70" s="4"/>
       <c r="M70" s="5">
-        <v>38406.748333333329</v>
+        <v>44123.419999999998</v>
       </c>
       <c r="N70" s="6">
-        <v>309</v>
+        <v>416</v>
       </c>
       <c r="O70" s="6">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="P70" s="7">
-        <v>3.260664308681672</v>
+        <v>3.4512329355608595</v>
       </c>
       <c r="Q70" s="8">
-        <v>10.685039759036144</v>
+        <v>11.006155855855855</v>
       </c>
       <c r="R70" s="8">
-        <v>2.8380715686274507</v>
+        <v>2.9029338028169014</v>
       </c>
       <c r="S70" s="8">
         <v>7</v>
       </c>
       <c r="T70" s="9">
-        <v>0.83734939759036142</v>
+        <v>0.82432432432432434</v>
       </c>
       <c r="U70" s="9">
-        <v>0.5</v>
+        <v>0.49099099099099097</v>
       </c>
       <c r="V70" s="9">
-        <v>0.006024096385542169</v>
+        <v>0.0045045045045045045</v>
       </c>
       <c r="W70" s="9">
         <v>0</v>
       </c>
       <c r="X70" s="9">
-        <v>0.054216867469879519</v>
+        <v>0.054054054054054057</v>
       </c>
       <c r="Y70" s="9">
-        <v>0.12650602409638553</v>
+        <v>0.11261261261261261</v>
       </c>
       <c r="Z70" s="9">
         <v>0</v>
       </c>
       <c r="AA70" s="9">
-        <v>0.44578313253012047</v>
+        <v>0.44144144144144143</v>
       </c>
       <c r="AB70" s="9">
-        <v>0.066265060240963861</v>
+        <v>0.04954954954954955</v>
       </c>
       <c r="AC70" s="9">
         <v>0</v>
       </c>
       <c r="AD70" s="6">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="AE70" s="6">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="AF70" s="6">
         <v>1</v>
@@ -12006,16 +12003,16 @@
         <v>0</v>
       </c>
       <c r="AH70" s="6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AI70" s="6">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AJ70" s="6">
         <v>0</v>
       </c>
       <c r="AK70" s="6">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AL70" s="6">
         <v>11</v>
@@ -12379,7 +12376,7 @@
         <v>19694</v>
       </c>
       <c r="B73" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C73" s="4">
         <v>51</v>
@@ -12410,85 +12407,85 @@
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="5">
-        <v>49140.186666666668</v>
+        <v>49657.710000000006</v>
       </c>
       <c r="N73" s="6">
-        <v>419</v>
+        <v>499</v>
       </c>
       <c r="O73" s="6">
-        <v>292</v>
+        <v>346</v>
       </c>
       <c r="P73" s="7">
-        <v>7.1830949880668262</v>
+        <v>6.6024818913480887</v>
       </c>
       <c r="Q73" s="8">
-        <v>29.598230479452056</v>
+        <v>29.708670520231216</v>
       </c>
       <c r="R73" s="8">
-        <v>15.531436896551723</v>
+        <v>16.204699709302325</v>
       </c>
       <c r="S73" s="8">
         <v>7</v>
       </c>
       <c r="T73" s="9">
-        <v>0.11986301369863013</v>
+        <v>0.10982658959537572</v>
       </c>
       <c r="U73" s="9">
-        <v>0.2226027397260274</v>
+        <v>0.21965317919075145</v>
       </c>
       <c r="V73" s="9">
-        <v>0.071917808219178078</v>
+        <v>0.06358381502890173</v>
       </c>
       <c r="W73" s="9">
-        <v>0.0034246575339999998</v>
+        <v>0.0028901734099999999</v>
       </c>
       <c r="X73" s="9">
-        <v>0.041095890410958902</v>
+        <v>0.049132947976878616</v>
       </c>
       <c r="Y73" s="9">
-        <v>0.0034246575342465752</v>
+        <v>0.0028901734104046241</v>
       </c>
       <c r="Z73" s="9">
-        <v>0</v>
+        <v>0.0028901734104046241</v>
       </c>
       <c r="AA73" s="9">
-        <v>0.013698630136986301</v>
+        <v>0.011560693641618497</v>
       </c>
       <c r="AB73" s="9">
-        <v>0.017123287671232876</v>
+        <v>0.017341040462427744</v>
       </c>
       <c r="AC73" s="9">
-        <v>0.095890410958904104</v>
+        <v>0.089595375722543349</v>
       </c>
       <c r="AD73" s="6">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="AE73" s="6">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="AF73" s="6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG73" s="6">
         <v>1</v>
       </c>
       <c r="AH73" s="6">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AI73" s="6">
         <v>1</v>
       </c>
       <c r="AJ73" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK73" s="6">
         <v>4</v>
       </c>
       <c r="AL73" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM73" s="6">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AN73" s="9">
         <v>0</v>
@@ -14926,7 +14923,7 @@
         <v>19730</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>51</v>
@@ -14955,67 +14952,67 @@
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="5">
-        <v>57734.903333333328</v>
+        <v>62360.949999999997</v>
       </c>
       <c r="N90" s="6">
-        <v>502</v>
+        <v>640</v>
       </c>
       <c r="O90" s="6">
-        <v>150</v>
+        <v>189</v>
       </c>
       <c r="P90" s="7">
-        <v>6.4565013861386138</v>
+        <v>6.1405795031055899</v>
       </c>
       <c r="Q90" s="8">
-        <v>22.940111333333334</v>
+        <v>23.887213756613757</v>
       </c>
       <c r="R90" s="8">
-        <v>8.9715879194630865</v>
+        <v>10.114715957446808</v>
       </c>
       <c r="S90" s="8">
         <v>8</v>
       </c>
       <c r="T90" s="9">
-        <v>0.13333333333333333</v>
+        <v>0.12169312169312169</v>
       </c>
       <c r="U90" s="9">
-        <v>0.26666666666666666</v>
+        <v>0.26455026455026454</v>
       </c>
       <c r="V90" s="9">
-        <v>0.02</v>
+        <v>0.021164021164021163</v>
       </c>
       <c r="W90" s="9">
-        <v>0</v>
+        <v>0.0052910052909999998</v>
       </c>
       <c r="X90" s="9">
-        <v>0.013333333333333334</v>
+        <v>0.010582010582010581</v>
       </c>
       <c r="Y90" s="9">
         <v>0</v>
       </c>
       <c r="Z90" s="9">
-        <v>0</v>
+        <v>0.0052910052910052907</v>
       </c>
       <c r="AA90" s="9">
-        <v>0.013333333333333334</v>
+        <v>0.010582010582010581</v>
       </c>
       <c r="AB90" s="9">
-        <v>0.040000000000000001</v>
+        <v>0.042328042328042326</v>
       </c>
       <c r="AC90" s="9">
-        <v>0.16</v>
+        <v>0.15873015873015872</v>
       </c>
       <c r="AD90" s="6">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="AE90" s="6">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AF90" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG90" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH90" s="6">
         <v>2</v>
@@ -15024,22 +15021,22 @@
         <v>0</v>
       </c>
       <c r="AJ90" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK90" s="6">
         <v>2</v>
       </c>
       <c r="AL90" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AM90" s="6">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AN90" s="9">
-        <v>0.026666666666666668</v>
+        <v>0.026455026455026454</v>
       </c>
       <c r="AO90" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c t="s" r="AP90" s="4">
         <v>58</v>
@@ -16430,7 +16427,7 @@
         <v>19749</v>
       </c>
       <c r="B100" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C100" s="4">
         <v>51</v>
@@ -16459,49 +16456,49 @@
       </c>
       <c r="L100" s="4"/>
       <c r="M100" s="5">
-        <v>30329.565000000002</v>
+        <v>31718.230000000003</v>
       </c>
       <c r="N100" s="6">
-        <v>277</v>
+        <v>342</v>
       </c>
       <c r="O100" s="6">
-        <v>152</v>
+        <v>191</v>
       </c>
       <c r="P100" s="7">
-        <v>9.1926340823970047</v>
+        <v>9.1982722560975603</v>
       </c>
       <c r="Q100" s="8">
-        <v>29.167873026315789</v>
+        <v>30.045637172774867</v>
       </c>
       <c r="R100" s="8">
-        <v>11.915667333333333</v>
+        <v>12.947884126984126</v>
       </c>
       <c r="S100" s="8">
         <v>8</v>
       </c>
       <c r="T100" s="9">
-        <v>0.10526315789473684</v>
+        <v>0.083769633507853408</v>
       </c>
       <c r="U100" s="9">
-        <v>0.10526315789473684</v>
+        <v>0.09947643979057591</v>
       </c>
       <c r="V100" s="9">
-        <v>0.078947368421052627</v>
+        <v>0.078534031413612565</v>
       </c>
       <c r="W100" s="9">
-        <v>0.0065789473680000002</v>
+        <v>0.0052356020940000003</v>
       </c>
       <c r="X100" s="9">
-        <v>0.039473684210526314</v>
+        <v>0.031413612565445025</v>
       </c>
       <c r="Y100" s="9">
-        <v>0.013157894736842105</v>
+        <v>0.010471204188481676</v>
       </c>
       <c r="Z100" s="9">
-        <v>0.0065789473684210523</v>
+        <v>0.005235602094240838</v>
       </c>
       <c r="AA100" s="9">
-        <v>0.013157894736842105</v>
+        <v>0.010471204188481676</v>
       </c>
       <c r="AB100" s="9">
         <v>0</v>
@@ -16510,13 +16507,13 @@
         <v>0</v>
       </c>
       <c r="AD100" s="6">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AE100" s="6">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AF100" s="6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AG100" s="6">
         <v>1</v>
@@ -16585,7 +16582,7 @@
         <v>19752</v>
       </c>
       <c r="B101" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C101" s="4">
         <v>51</v>
@@ -16614,64 +16611,64 @@
       </c>
       <c r="L101" s="4"/>
       <c r="M101" s="5">
-        <v>25637.394999999993</v>
+        <v>27214.859999999997</v>
       </c>
       <c r="N101" s="6">
-        <v>243</v>
+        <v>301</v>
       </c>
       <c r="O101" s="6">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="P101" s="7">
-        <v>6.1071224066390037</v>
+        <v>6.7369558528428088</v>
       </c>
       <c r="Q101" s="8">
-        <v>22.256134027777776</v>
+        <v>22.611177245508983</v>
       </c>
       <c r="R101" s="8">
-        <v>10.134543548387096</v>
+        <v>9.8377557823129251</v>
       </c>
       <c r="S101" s="8">
         <v>8</v>
       </c>
       <c r="T101" s="9">
-        <v>0.25</v>
+        <v>0.21556886227544911</v>
       </c>
       <c r="U101" s="9">
-        <v>0.40689655172413791</v>
+        <v>0.39644970414201186</v>
       </c>
       <c r="V101" s="9">
-        <v>0.089655172413793102</v>
+        <v>0.11242603550295859</v>
       </c>
       <c r="W101" s="9">
         <v>0</v>
       </c>
       <c r="X101" s="9">
-        <v>0.027586206896551724</v>
+        <v>0.023668639053254437</v>
       </c>
       <c r="Y101" s="9">
-        <v>0.020689655172413793</v>
+        <v>0.017751479289940829</v>
       </c>
       <c r="Z101" s="9">
-        <v>0.0068965517241379309</v>
+        <v>0.0059171597633136093</v>
       </c>
       <c r="AA101" s="9">
-        <v>0.15862068965517243</v>
+        <v>0.13609467455621302</v>
       </c>
       <c r="AB101" s="9">
-        <v>0.055172413793103448</v>
+        <v>0.047337278106508875</v>
       </c>
       <c r="AC101" s="9">
-        <v>0.13793103448275862</v>
+        <v>0.13017751479289941</v>
       </c>
       <c r="AD101" s="6">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="AE101" s="6">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="AF101" s="6">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AG101" s="6">
         <v>0</v>
@@ -16692,7 +16689,7 @@
         <v>8</v>
       </c>
       <c r="AM101" s="6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AN101" s="9">
         <v>0</v>
@@ -16897,7 +16894,7 @@
         <v>19754</v>
       </c>
       <c r="B103" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C103" s="4">
         <v>51</v>
@@ -16928,70 +16925,70 @@
       </c>
       <c r="L103" s="4"/>
       <c r="M103" s="5">
-        <v>61619.366666666676</v>
+        <v>66790.630000000005</v>
       </c>
       <c r="N103" s="6">
-        <v>527</v>
+        <v>673</v>
       </c>
       <c r="O103" s="6">
-        <v>305</v>
+        <v>392</v>
       </c>
       <c r="P103" s="7">
-        <v>2.547731379962193</v>
+        <v>2.5514747787610617</v>
       </c>
       <c r="Q103" s="8">
-        <v>15.558688852459015</v>
+        <v>15.842092091836733</v>
       </c>
       <c r="R103" s="8">
-        <v>4.9311950657894741</v>
+        <v>5.2410256410256411</v>
       </c>
       <c r="S103" s="8">
         <v>8</v>
       </c>
       <c r="T103" s="9">
-        <v>0.52131147540983602</v>
+        <v>0.50510204081632648</v>
       </c>
       <c r="U103" s="9">
-        <v>0.078688524590163941</v>
+        <v>0.091836734693877556</v>
       </c>
       <c r="V103" s="9">
-        <v>0.036065573770491806</v>
+        <v>0.03826530612244898</v>
       </c>
       <c r="W103" s="9">
         <v>0</v>
       </c>
       <c r="X103" s="9">
-        <v>0.029508196721311476</v>
+        <v>0.025510204081632654</v>
       </c>
       <c r="Y103" s="9">
         <v>0</v>
       </c>
       <c r="Z103" s="9">
-        <v>0.0032786885245901639</v>
+        <v>0.0025510204081632651</v>
       </c>
       <c r="AA103" s="9">
-        <v>0.0032786885245901639</v>
+        <v>0.0051020408163265302</v>
       </c>
       <c r="AB103" s="9">
-        <v>0.0098360655737704927</v>
+        <v>0.017857142857142856</v>
       </c>
       <c r="AC103" s="9">
-        <v>0</v>
+        <v>0.01020408163265306</v>
       </c>
       <c r="AD103" s="6">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="AE103" s="6">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="AF103" s="6">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AG103" s="6">
         <v>0</v>
       </c>
       <c r="AH103" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI103" s="6">
         <v>0</v>
@@ -17000,13 +16997,13 @@
         <v>1</v>
       </c>
       <c r="AK103" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL103" s="6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AM103" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN103" s="9">
         <v>0</v>
@@ -18504,7 +18501,7 @@
         <v>321</v>
       </c>
       <c r="O113" s="6">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="P113" s="7">
         <v>6.2194273006134972</v>
@@ -18522,46 +18519,46 @@
         <v>0.2807017543859649</v>
       </c>
       <c r="U113" s="9">
-        <v>0.46721311475409838</v>
+        <v>0.36257309941520466</v>
       </c>
       <c r="V113" s="9">
-        <v>0.073770491803278687</v>
+        <v>0.058479532163742687</v>
       </c>
       <c r="W113" s="9">
-        <v>0.016393442622000001</v>
+        <v>0.011695906432000001</v>
       </c>
       <c r="X113" s="9">
-        <v>0.05737704918032787</v>
+        <v>0.058479532163742687</v>
       </c>
       <c r="Y113" s="9">
-        <v>0.049180327868852458</v>
+        <v>0.035087719298245612</v>
       </c>
       <c r="Z113" s="9">
         <v>0</v>
       </c>
       <c r="AA113" s="9">
-        <v>0.28688524590163933</v>
+        <v>0.21052631578947367</v>
       </c>
       <c r="AB113" s="9">
-        <v>0.0081967213114754103</v>
+        <v>0.0058479532163742687</v>
       </c>
       <c r="AC113" s="9">
-        <v>0.10655737704918032</v>
+        <v>0.076023391812865493</v>
       </c>
       <c r="AD113" s="6">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="AE113" s="6">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="AF113" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG113" s="6">
         <v>2</v>
       </c>
       <c r="AH113" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AI113" s="6">
         <v>6</v>
@@ -18570,7 +18567,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="6">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AL113" s="6">
         <v>1</v>
@@ -21419,7 +21416,7 @@
         <v>264</v>
       </c>
       <c r="O132" s="6">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="P132" s="7">
         <v>7.1985188888888896</v>
@@ -21437,7 +21434,7 @@
         <v>0.36021505376344087</v>
       </c>
       <c r="U132" s="9">
-        <v>0.2709677419354839</v>
+        <v>0.29569892473118281</v>
       </c>
       <c r="V132" s="9">
         <v>0</v>
@@ -21446,28 +21443,28 @@
         <v>0</v>
       </c>
       <c r="X132" s="9">
-        <v>0.051612903225806452</v>
+        <v>0.069892473118279563</v>
       </c>
       <c r="Y132" s="9">
-        <v>0.0064516129032258064</v>
+        <v>0.016129032258064516</v>
       </c>
       <c r="Z132" s="9">
         <v>0</v>
       </c>
       <c r="AA132" s="9">
-        <v>0.21935483870967742</v>
+        <v>0.23118279569892472</v>
       </c>
       <c r="AB132" s="9">
-        <v>0.01935483870967742</v>
+        <v>0.016129032258064516</v>
       </c>
       <c r="AC132" s="9">
-        <v>0.012903225806451613</v>
+        <v>0.010752688172043012</v>
       </c>
       <c r="AD132" s="6">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="AE132" s="6">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AF132" s="6">
         <v>0</v>
@@ -21476,16 +21473,16 @@
         <v>0</v>
       </c>
       <c r="AH132" s="6">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AI132" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ132" s="6">
         <v>0</v>
       </c>
       <c r="AK132" s="6">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="AL132" s="6">
         <v>3</v>
@@ -24338,7 +24335,7 @@
         <v>274</v>
       </c>
       <c r="O151" s="6">
-        <v>67</v>
+        <v>235</v>
       </c>
       <c r="P151" s="7">
         <v>6.373504029304029</v>
@@ -24356,61 +24353,61 @@
         <v>0.28936170212765955</v>
       </c>
       <c r="U151" s="9">
-        <v>0.13432835820895522</v>
+        <v>0.18723404255319148</v>
       </c>
       <c r="V151" s="9">
-        <v>0.029850746268656716</v>
+        <v>0.034042553191489362</v>
       </c>
       <c r="W151" s="9">
         <v>0</v>
       </c>
       <c r="X151" s="9">
-        <v>0.014925373134328358</v>
+        <v>0.02553191489361702</v>
       </c>
       <c r="Y151" s="9">
-        <v>0</v>
+        <v>0.0042553191489361703</v>
       </c>
       <c r="Z151" s="9">
         <v>0</v>
       </c>
       <c r="AA151" s="9">
-        <v>0.014925373134328358</v>
+        <v>0.089361702127659579</v>
       </c>
       <c r="AB151" s="9">
-        <v>0.014925373134328358</v>
+        <v>0.01276595744680851</v>
       </c>
       <c r="AC151" s="9">
-        <v>0.059701492537313432</v>
+        <v>0.02553191489361702</v>
       </c>
       <c r="AD151" s="6">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="AE151" s="6">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="AF151" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AG151" s="6">
         <v>0</v>
       </c>
       <c r="AH151" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AI151" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ151" s="6">
         <v>0</v>
       </c>
       <c r="AK151" s="6">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="AL151" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AM151" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN151" s="9">
         <v>0</v>
@@ -24772,7 +24769,7 @@
         <v>19898</v>
       </c>
       <c r="B154" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c t="s" r="C154" s="4">
         <v>51</v>
@@ -24801,88 +24798,88 @@
       </c>
       <c r="L154" s="4"/>
       <c r="M154" s="5">
-        <v>13522.32</v>
+        <v>15389.319999999998</v>
       </c>
       <c r="N154" s="6">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="O154" s="6">
-        <v>54</v>
+        <v>111</v>
       </c>
       <c r="P154" s="7">
-        <v>2.9956032967032966</v>
+        <v>3.4519752577319589</v>
       </c>
       <c r="Q154" s="8">
-        <v>16.260185185185183</v>
+        <v>19.926126126126128</v>
       </c>
       <c r="R154" s="8">
-        <v>6.6408792452830196</v>
+        <v>9.855351376146789</v>
       </c>
       <c r="S154" s="8">
         <v>7</v>
       </c>
       <c r="T154" s="9">
-        <v>0.55555555555555558</v>
+        <v>0.36036036036036034</v>
       </c>
       <c r="U154" s="9">
-        <v>0.18518518518518517</v>
+        <v>0.21621621621621623</v>
       </c>
       <c r="V154" s="9">
-        <v>0.07407407407407407</v>
+        <v>0.072072072072072071</v>
       </c>
       <c r="W154" s="9">
         <v>0</v>
       </c>
       <c r="X154" s="9">
-        <v>0.055555555555555552</v>
+        <v>0.036036036036036036</v>
       </c>
       <c r="Y154" s="9">
-        <v>0</v>
+        <v>0.0090090090090090089</v>
       </c>
       <c r="Z154" s="9">
         <v>0</v>
       </c>
       <c r="AA154" s="9">
-        <v>0.07407407407407407</v>
+        <v>0.045045045045045043</v>
       </c>
       <c r="AB154" s="9">
-        <v>0.018518518518518517</v>
+        <v>0.018018018018018018</v>
       </c>
       <c r="AC154" s="9">
-        <v>0</v>
+        <v>0.063063063063063057</v>
       </c>
       <c r="AD154" s="6">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="AE154" s="6">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="AF154" s="6">
+        <v>8</v>
+      </c>
+      <c r="AG154" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH154" s="6">
         <v>4</v>
       </c>
-      <c r="AG154" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH154" s="6">
-        <v>3</v>
-      </c>
       <c r="AI154" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ154" s="6">
         <v>0</v>
       </c>
       <c r="AK154" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL154" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM154" s="6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AN154" s="9">
-        <v>0.018518518518518517</v>
+        <v>0.0090090090090090089</v>
       </c>
       <c r="AO154" s="6">
         <v>1</v>
@@ -25276,7 +25273,7 @@
         <v>587</v>
       </c>
       <c r="O157" s="6">
-        <v>195</v>
+        <v>283</v>
       </c>
       <c r="P157" s="7">
         <v>6.3254766031195846</v>
@@ -25294,25 +25291,25 @@
         <v>0.62190812720848054</v>
       </c>
       <c r="U157" s="9">
-        <v>0.030769230769230771</v>
+        <v>0.021201413427561839</v>
       </c>
       <c r="V157" s="9">
-        <v>0.0051282051282051282</v>
+        <v>0.0035335689045936395</v>
       </c>
       <c r="W157" s="9">
         <v>0</v>
       </c>
       <c r="X157" s="9">
-        <v>0.02564102564102564</v>
+        <v>0.017667844522968199</v>
       </c>
       <c r="Y157" s="9">
-        <v>0.0051282051282051282</v>
+        <v>0.0035335689045936395</v>
       </c>
       <c r="Z157" s="9">
         <v>0</v>
       </c>
       <c r="AA157" s="9">
-        <v>0.0051282051282051282</v>
+        <v>0.0035335689045936395</v>
       </c>
       <c r="AB157" s="9">
         <v>0</v>
@@ -26592,7 +26589,7 @@
         <v>19927</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C166" s="4">
         <v>51</v>
@@ -26623,34 +26620,34 @@
       </c>
       <c r="L166" s="4"/>
       <c r="M166" s="5">
-        <v>10608.196666666667</v>
+        <v>12048.09</v>
       </c>
       <c r="N166" s="6">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="O166" s="6">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="P166" s="7">
-        <v>7.4154572580645164</v>
+        <v>8.5958079754601222</v>
       </c>
       <c r="Q166" s="8">
-        <v>22.433146067415731</v>
+        <v>24.063498347107441</v>
       </c>
       <c r="R166" s="8">
-        <v>8.781418390804598</v>
+        <v>9.1209410256410255</v>
       </c>
       <c r="S166" s="8">
         <v>7</v>
       </c>
       <c r="T166" s="9">
-        <v>0.15730337078651685</v>
+        <v>0.14049586776859505</v>
       </c>
       <c r="U166" s="9">
-        <v>0.10112359550561797</v>
+        <v>0.13223140495867769</v>
       </c>
       <c r="V166" s="9">
-        <v>0.078651685393258425</v>
+        <v>0.082644628099173556</v>
       </c>
       <c r="W166" s="9">
         <v>0</v>
@@ -26665,22 +26662,22 @@
         <v>0</v>
       </c>
       <c r="AA166" s="9">
-        <v>0.02247191011235955</v>
+        <v>0.033057851239669422</v>
       </c>
       <c r="AB166" s="9">
-        <v>0</v>
+        <v>0.016528925619834711</v>
       </c>
       <c r="AC166" s="9">
         <v>0</v>
       </c>
       <c r="AD166" s="6">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE166" s="6">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AF166" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG166" s="6">
         <v>0</v>
@@ -26695,10 +26692,10 @@
         <v>0</v>
       </c>
       <c r="AK166" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL166" s="6">
         <v>2</v>
-      </c>
-      <c r="AL166" s="6">
-        <v>0</v>
       </c>
       <c r="AM166" s="6">
         <v>0</v>
@@ -26749,7 +26746,7 @@
         <v>19928</v>
       </c>
       <c r="B167" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C167" s="4">
         <v>51</v>
@@ -26780,85 +26777,85 @@
       </c>
       <c r="L167" s="4"/>
       <c r="M167" s="5">
-        <v>26917.800000000003</v>
+        <v>27814.060000000001</v>
       </c>
       <c r="N167" s="6">
-        <v>263</v>
+        <v>317</v>
       </c>
       <c r="O167" s="6">
-        <v>186</v>
+        <v>230</v>
       </c>
       <c r="P167" s="7">
-        <v>5.1864620689655174</v>
+        <v>4.9053268987341774</v>
       </c>
       <c r="Q167" s="8">
-        <v>18.707706451612903</v>
+        <v>17.65565260869565</v>
       </c>
       <c r="R167" s="8">
-        <v>7.6579545454545448</v>
+        <v>6.8995348837209303</v>
       </c>
       <c r="S167" s="8">
         <v>7</v>
       </c>
       <c r="T167" s="9">
-        <v>0.44086021505376344</v>
+        <v>0.4826086956521739</v>
       </c>
       <c r="U167" s="9">
-        <v>0.25268817204301075</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="V167" s="9">
-        <v>0.016129032258064516</v>
+        <v>0.017391304347826087</v>
       </c>
       <c r="W167" s="9">
         <v>0</v>
       </c>
       <c r="X167" s="9">
-        <v>0.075268817204301078</v>
+        <v>0.069565217391304349</v>
       </c>
       <c r="Y167" s="9">
-        <v>0.010752688172043012</v>
+        <v>0.017391304347826087</v>
       </c>
       <c r="Z167" s="9">
         <v>0</v>
       </c>
       <c r="AA167" s="9">
-        <v>0.075268817204301078</v>
+        <v>0.091304347826086957</v>
       </c>
       <c r="AB167" s="9">
-        <v>0.043010752688172046</v>
+        <v>0.039130434782608699</v>
       </c>
       <c r="AC167" s="9">
-        <v>0.086021505376344093</v>
+        <v>0.095652173913043481</v>
       </c>
       <c r="AD167" s="6">
-        <v>57</v>
+        <v>76</v>
       </c>
       <c r="AE167" s="6">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="AF167" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG167" s="6">
         <v>0</v>
       </c>
       <c r="AH167" s="6">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AI167" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ167" s="6">
         <v>0</v>
       </c>
       <c r="AK167" s="6">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AL167" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM167" s="6">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AN167" s="9">
         <v>0</v>
@@ -26906,7 +26903,7 @@
         <v>19930</v>
       </c>
       <c r="B168" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C168" s="4">
         <v>51</v>
@@ -26937,40 +26934,40 @@
       </c>
       <c r="L168" s="4"/>
       <c r="M168" s="5">
-        <v>31574.64333333333</v>
+        <v>34377.979999999996</v>
       </c>
       <c r="N168" s="6">
-        <v>337</v>
+        <v>422</v>
       </c>
       <c r="O168" s="6">
-        <v>267</v>
+        <v>340</v>
       </c>
       <c r="P168" s="7">
-        <v>4.3374631268436579</v>
+        <v>4.4237983451536644</v>
       </c>
       <c r="Q168" s="8">
-        <v>21.61654194756554</v>
+        <v>21.392598235294116</v>
       </c>
       <c r="R168" s="8">
-        <v>10.639330681818182</v>
+        <v>10.24272997032641</v>
       </c>
       <c r="S168" s="8">
         <v>7</v>
       </c>
       <c r="T168" s="9">
-        <v>0.16104868913857678</v>
+        <v>0.14411764705882352</v>
       </c>
       <c r="U168" s="9">
-        <v>0.25093632958801498</v>
+        <v>0.22941176470588234</v>
       </c>
       <c r="V168" s="9">
-        <v>0.014981273408239701</v>
+        <v>0.011764705882352941</v>
       </c>
       <c r="W168" s="9">
         <v>0</v>
       </c>
       <c r="X168" s="9">
-        <v>0.037453183520599252</v>
+        <v>0.032352941176470591</v>
       </c>
       <c r="Y168" s="9">
         <v>0</v>
@@ -26979,19 +26976,19 @@
         <v>0</v>
       </c>
       <c r="AA168" s="9">
-        <v>0.011235955056179775</v>
+        <v>0.0088235294117647058</v>
       </c>
       <c r="AB168" s="9">
-        <v>0.0074906367041198503</v>
+        <v>0.011764705882352941</v>
       </c>
       <c r="AC168" s="9">
-        <v>0.18352059925093633</v>
+        <v>0.1676470588235294</v>
       </c>
       <c r="AD168" s="6">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="AE168" s="6">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="AF168" s="6">
         <v>4</v>
@@ -27000,7 +26997,7 @@
         <v>0</v>
       </c>
       <c r="AH168" s="6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI168" s="6">
         <v>0</v>
@@ -27012,10 +27009,10 @@
         <v>3</v>
       </c>
       <c r="AL168" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM168" s="6">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="AN168" s="9">
         <v>0</v>
@@ -27063,7 +27060,7 @@
         <v>19931</v>
       </c>
       <c r="B169" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C169" s="4">
         <v>51</v>
@@ -27094,85 +27091,85 @@
       </c>
       <c r="L169" s="4"/>
       <c r="M169" s="5">
-        <v>28476.746666666662</v>
+        <v>34695.910000000003</v>
       </c>
       <c r="N169" s="6">
-        <v>280</v>
+        <v>388</v>
       </c>
       <c r="O169" s="6">
-        <v>104</v>
+        <v>153</v>
       </c>
       <c r="P169" s="7">
-        <v>4.5436512820512815</v>
+        <v>4.5624348167539273</v>
       </c>
       <c r="Q169" s="8">
-        <v>15.745351923076923</v>
+        <v>15.975381045751632</v>
       </c>
       <c r="R169" s="8">
-        <v>4.3039916666666667</v>
+        <v>4.515267132867133</v>
       </c>
       <c r="S169" s="8">
         <v>7</v>
       </c>
       <c r="T169" s="9">
-        <v>0.51923076923076927</v>
+        <v>0.47712418300653597</v>
       </c>
       <c r="U169" s="9">
-        <v>0.19230769230769232</v>
+        <v>0.18300653594771241</v>
       </c>
       <c r="V169" s="9">
-        <v>0.019230769230769232</v>
+        <v>0.019607843137254902</v>
       </c>
       <c r="W169" s="9">
         <v>0</v>
       </c>
       <c r="X169" s="9">
-        <v>0.11538461538461539</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="Y169" s="9">
-        <v>0.028846153846153848</v>
+        <v>0.032679738562091505</v>
       </c>
       <c r="Z169" s="9">
         <v>0</v>
       </c>
       <c r="AA169" s="9">
-        <v>0.11538461538461539</v>
+        <v>0.091503267973856203</v>
       </c>
       <c r="AB169" s="9">
-        <v>0.019230769230769232</v>
+        <v>0.026143790849673203</v>
       </c>
       <c r="AC169" s="9">
-        <v>0</v>
+        <v>0.013071895424836602</v>
       </c>
       <c r="AD169" s="6">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="AE169" s="6">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AF169" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG169" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH169" s="6">
+        <v>17</v>
+      </c>
+      <c r="AI169" s="6">
+        <v>5</v>
+      </c>
+      <c r="AJ169" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK169" s="6">
+        <v>14</v>
+      </c>
+      <c r="AL169" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM169" s="6">
         <v>2</v>
-      </c>
-      <c r="AG169" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH169" s="6">
-        <v>12</v>
-      </c>
-      <c r="AI169" s="6">
-        <v>3</v>
-      </c>
-      <c r="AJ169" s="6">
-        <v>0</v>
-      </c>
-      <c r="AK169" s="6">
-        <v>12</v>
-      </c>
-      <c r="AL169" s="6">
-        <v>2</v>
-      </c>
-      <c r="AM169" s="6">
-        <v>0</v>
       </c>
       <c r="AN169" s="9">
         <v>0</v>
@@ -27689,7 +27686,7 @@
         <v>19943</v>
       </c>
       <c r="B173" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C173" s="4">
         <v>51</v>
@@ -27720,55 +27717,55 @@
       </c>
       <c r="L173" s="4"/>
       <c r="M173" s="5">
-        <v>17475.710000000003</v>
+        <v>18915.139999999996</v>
       </c>
       <c r="N173" s="6">
-        <v>190</v>
+        <v>237</v>
       </c>
       <c r="O173" s="6">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="P173" s="7">
-        <v>7.7055845744680846</v>
+        <v>7.4994323404255319</v>
       </c>
       <c r="Q173" s="8">
-        <v>19.814833027522937</v>
+        <v>20.07676893939394</v>
       </c>
       <c r="R173" s="8">
-        <v>6.8063504761904756</v>
+        <v>7.0165375000000001</v>
       </c>
       <c r="S173" s="8">
         <v>7</v>
       </c>
       <c r="T173" s="9">
-        <v>0.26605504587155965</v>
+        <v>0.24242424242424243</v>
       </c>
       <c r="U173" s="9">
-        <v>0.15596330275229359</v>
+        <v>0.12878787878787878</v>
       </c>
       <c r="V173" s="9">
-        <v>0.01834862385321101</v>
+        <v>0.015151515151515152</v>
       </c>
       <c r="W173" s="9">
         <v>0</v>
       </c>
       <c r="X173" s="9">
-        <v>0.082568807339449546</v>
+        <v>0.068181818181818177</v>
       </c>
       <c r="Y173" s="9">
-        <v>0.01834862385321101</v>
+        <v>0.015151515151515152</v>
       </c>
       <c r="Z173" s="9">
-        <v>0.0091743119266055051</v>
+        <v>0.007575757575757576</v>
       </c>
       <c r="AA173" s="9">
-        <v>0.045871559633027525</v>
+        <v>0.03787878787878788</v>
       </c>
       <c r="AB173" s="9">
-        <v>0.01834862385321101</v>
+        <v>0.015151515151515152</v>
       </c>
       <c r="AC173" s="9">
-        <v>0.01834862385321101</v>
+        <v>0.015151515151515152</v>
       </c>
       <c r="AD173" s="6">
         <v>23</v>
@@ -28631,7 +28628,7 @@
         <v>19954</v>
       </c>
       <c r="B179" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C179" s="4">
         <v>51</v>
@@ -28662,40 +28659,40 @@
       </c>
       <c r="L179" s="4"/>
       <c r="M179" s="5">
-        <v>11691.528333333335</v>
+        <v>15001.980000000001</v>
       </c>
       <c r="N179" s="6">
-        <v>129</v>
+        <v>193</v>
       </c>
       <c r="O179" s="6">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="P179" s="7">
-        <v>6.7216148437500003</v>
+        <v>7.7970489583333338</v>
       </c>
       <c r="Q179" s="8">
-        <v>18.122805263157897</v>
+        <v>18.628276404494382</v>
       </c>
       <c r="R179" s="8">
-        <v>3.9856719298245613</v>
+        <v>4.1503741573033714</v>
       </c>
       <c r="S179" s="8">
         <v>7</v>
       </c>
       <c r="T179" s="9">
-        <v>0.45614035087719296</v>
+        <v>0.43820224719101125</v>
       </c>
       <c r="U179" s="9">
-        <v>0.08771929824561403</v>
+        <v>0.0898876404494382</v>
       </c>
       <c r="V179" s="9">
-        <v>0.070175438596491224</v>
+        <v>0.056179775280898875</v>
       </c>
       <c r="W179" s="9">
-        <v>0.017543859649000001</v>
+        <v>0.011235955056</v>
       </c>
       <c r="X179" s="9">
-        <v>0.035087719298245612</v>
+        <v>0.033707865168539325</v>
       </c>
       <c r="Y179" s="9">
         <v>0</v>
@@ -28704,28 +28701,28 @@
         <v>0</v>
       </c>
       <c r="AA179" s="9">
-        <v>0</v>
+        <v>0.011235955056179775</v>
       </c>
       <c r="AB179" s="9">
-        <v>0.017543859649122806</v>
+        <v>0.011235955056179775</v>
       </c>
       <c r="AC179" s="9">
         <v>0</v>
       </c>
       <c r="AD179" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE179" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF179" s="6">
         <v>5</v>
       </c>
-      <c r="AF179" s="6">
-        <v>4</v>
-      </c>
       <c r="AG179" s="6">
         <v>1</v>
       </c>
       <c r="AH179" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI179" s="6">
         <v>0</v>
@@ -28734,7 +28731,7 @@
         <v>0</v>
       </c>
       <c r="AK179" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL179" s="6">
         <v>1</v>
@@ -29102,7 +29099,7 @@
         <v>19959</v>
       </c>
       <c r="B182" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C182" s="4">
         <v>51</v>
@@ -29133,40 +29130,40 @@
       </c>
       <c r="L182" s="4"/>
       <c r="M182" s="5">
-        <v>14748.125</v>
+        <v>18255.450000000001</v>
       </c>
       <c r="N182" s="6">
-        <v>148</v>
+        <v>204</v>
       </c>
       <c r="O182" s="6">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="P182" s="7">
-        <v>4.9819156028368798</v>
+        <v>5.649830612244898</v>
       </c>
       <c r="Q182" s="8">
-        <v>16.967968750000001</v>
+        <v>16.642181481481479</v>
       </c>
       <c r="R182" s="8">
-        <v>5.2502650793650796</v>
+        <v>4.6919835443037972</v>
       </c>
       <c r="S182" s="8">
         <v>7</v>
       </c>
       <c r="T182" s="9">
-        <v>0.46875</v>
+        <v>0.49382716049382713</v>
       </c>
       <c r="U182" s="9">
-        <v>0.15625</v>
+        <v>0.16049382716049382</v>
       </c>
       <c r="V182" s="9">
-        <v>0.078125</v>
+        <v>0.07407407407407407</v>
       </c>
       <c r="W182" s="9">
         <v>0</v>
       </c>
       <c r="X182" s="9">
-        <v>0</v>
+        <v>0.012345679012345678</v>
       </c>
       <c r="Y182" s="9">
         <v>0</v>
@@ -29175,37 +29172,37 @@
         <v>0</v>
       </c>
       <c r="AA182" s="9">
-        <v>0.046875</v>
+        <v>0.061728395061728392</v>
       </c>
       <c r="AB182" s="9">
-        <v>0.03125</v>
+        <v>0.024691358024691357</v>
       </c>
       <c r="AC182" s="9">
         <v>0</v>
       </c>
       <c r="AD182" s="6">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AE182" s="6">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AF182" s="6">
+        <v>6</v>
+      </c>
+      <c r="AG182" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH182" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI182" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ182" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK182" s="6">
         <v>5</v>
-      </c>
-      <c r="AG182" s="6">
-        <v>0</v>
-      </c>
-      <c r="AH182" s="6">
-        <v>0</v>
-      </c>
-      <c r="AI182" s="6">
-        <v>0</v>
-      </c>
-      <c r="AJ182" s="6">
-        <v>0</v>
-      </c>
-      <c r="AK182" s="6">
-        <v>3</v>
       </c>
       <c r="AL182" s="6">
         <v>2</v>
@@ -29259,7 +29256,7 @@
         <v>19961</v>
       </c>
       <c r="B183" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C183" s="4">
         <v>51</v>
@@ -29290,82 +29287,82 @@
       </c>
       <c r="L183" s="4"/>
       <c r="M183" s="5">
-        <v>18499.063333333335</v>
+        <v>20894.170000000002</v>
       </c>
       <c r="N183" s="6">
-        <v>179</v>
+        <v>230</v>
       </c>
       <c r="O183" s="6">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="P183" s="7">
-        <v>6.1321833333333338</v>
+        <v>6.0183031250000001</v>
       </c>
       <c r="Q183" s="8">
-        <v>16.492095876288662</v>
+        <v>16.221774193548388</v>
       </c>
       <c r="R183" s="8">
-        <v>3.3527173913043478</v>
+        <v>3.4462965811965813</v>
       </c>
       <c r="S183" s="8">
         <v>7</v>
       </c>
       <c r="T183" s="9">
-        <v>0.46391752577319589</v>
+        <v>0.45967741935483869</v>
       </c>
       <c r="U183" s="9">
-        <v>0.14432989690721648</v>
+        <v>0.16129032258064516</v>
       </c>
       <c r="V183" s="9">
-        <v>0.010309278350515464</v>
+        <v>0.024193548387096774</v>
       </c>
       <c r="W183" s="9">
         <v>0</v>
       </c>
       <c r="X183" s="9">
-        <v>0.020618556701030927</v>
+        <v>0.024193548387096774</v>
       </c>
       <c r="Y183" s="9">
-        <v>0.010309278350515464</v>
+        <v>0.016129032258064516</v>
       </c>
       <c r="Z183" s="9">
-        <v>0.010309278350515464</v>
+        <v>0.0080645161290322578</v>
       </c>
       <c r="AA183" s="9">
-        <v>0.08247422680412371</v>
+        <v>0.096774193548387094</v>
       </c>
       <c r="AB183" s="9">
-        <v>0.030927835051546393</v>
+        <v>0.032258064516129031</v>
       </c>
       <c r="AC183" s="9">
-        <v>0.020618556701030927</v>
+        <v>0.016129032258064516</v>
       </c>
       <c r="AD183" s="6">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AE183" s="6">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AF183" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AG183" s="6">
         <v>0</v>
       </c>
       <c r="AH183" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI183" s="6">
         <v>2</v>
       </c>
-      <c r="AI183" s="6">
-        <v>1</v>
-      </c>
       <c r="AJ183" s="6">
         <v>1</v>
       </c>
       <c r="AK183" s="6">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AL183" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM183" s="6">
         <v>2</v>
@@ -30137,52 +30134,52 @@
         <v>312</v>
       </c>
       <c t="s" r="Z189" s="11">
+        <v>310</v>
+      </c>
+      <c t="s" r="AA189" s="11">
         <v>313</v>
       </c>
-      <c t="s" r="AA189" s="11">
+      <c t="s" r="AB189" s="11">
         <v>314</v>
       </c>
-      <c t="s" r="AB189" s="11">
+      <c t="s" r="AC189" s="11">
         <v>315</v>
       </c>
-      <c t="s" r="AC189" s="11">
+      <c t="s" r="AD189" s="11">
         <v>316</v>
       </c>
-      <c t="s" r="AD189" s="11">
+      <c t="s" r="AE189" s="11">
         <v>317</v>
       </c>
-      <c t="s" r="AE189" s="11">
+      <c t="s" r="AF189" s="11">
         <v>318</v>
       </c>
-      <c t="s" r="AF189" s="11">
+      <c t="s" r="AG189" s="11">
         <v>319</v>
       </c>
-      <c t="s" r="AG189" s="11">
+      <c t="s" r="AH189" s="11">
         <v>320</v>
       </c>
-      <c t="s" r="AH189" s="11">
+      <c t="s" r="AI189" s="11">
         <v>321</v>
       </c>
-      <c t="s" r="AI189" s="11">
+      <c t="s" r="AJ189" s="11">
         <v>322</v>
       </c>
-      <c t="s" r="AJ189" s="11">
+      <c t="s" r="AK189" s="11">
         <v>323</v>
       </c>
-      <c t="s" r="AK189" s="11">
+      <c t="s" r="AL189" s="11">
         <v>324</v>
       </c>
-      <c t="s" r="AL189" s="11">
+      <c t="s" r="AM189" s="11">
         <v>325</v>
       </c>
-      <c t="s" r="AM189" s="11">
+      <c t="s" r="AN189" s="11">
         <v>326</v>
       </c>
-      <c t="s" r="AN189" s="11">
+      <c t="s" r="AO189" s="11">
         <v>327</v>
-      </c>
-      <c t="s" r="AO189" s="11">
-        <v>328</v>
       </c>
       <c r="AP189" s="12"/>
       <c t="s" r="AQ189" s="12">
@@ -30199,10 +30196,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX189" s="11">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c t="s" r="AY189" s="11">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AZ189" s="12"/>
       <c r="BA189" s="12"/>

--- a/franquias/pwr_reports/KEYS Service Main Service Exceptions - Franquias (Stores)(2026-08-03 - 2026-08-09).xlsx
+++ b/franquias/pwr_reports/KEYS Service Main Service Exceptions - Franquias (Stores)(2026-08-03 - 2026-08-09).xlsx
@@ -710,129 +710,132 @@
     <t>VERVLOET,HUGO LEONARDO LOUZADA</t>
   </si>
   <si>
+    <t>DURANTE,RAFAEL BARROS</t>
+  </si>
+  <si>
+    <t>Guarujá</t>
+  </si>
+  <si>
+    <t>MANAUS</t>
+  </si>
+  <si>
+    <t>BRASILIA</t>
+  </si>
+  <si>
+    <t>Risuenho,Igor and Vinicius Costa</t>
+  </si>
+  <si>
+    <t>Canoas</t>
+  </si>
+  <si>
+    <t>Guarulhos</t>
+  </si>
+  <si>
+    <t>RYNALDO CALSAVARA,ANDRE</t>
+  </si>
+  <si>
+    <t>PETROLINA</t>
+  </si>
+  <si>
+    <t>Coelho,Caio Bezerra de Souza</t>
+  </si>
+  <si>
+    <t>TAGUATINGA</t>
+  </si>
+  <si>
+    <t>MONTES CLAROS</t>
+  </si>
+  <si>
+    <t>MARTINS,RODRIGO LUIS and WILSON ATHAYDE RIBEIRO</t>
+  </si>
+  <si>
+    <t>FORTALEZA</t>
+  </si>
+  <si>
+    <t>VARGINHA</t>
+  </si>
+  <si>
+    <t>Poloni,Gabriel Godoy</t>
+  </si>
+  <si>
+    <t>ARMACAO DOS BUZIOS</t>
+  </si>
+  <si>
+    <t>DE ALMEIDA,MATHEUS OLIVEIRA</t>
+  </si>
+  <si>
+    <t>LUIS EDUARDO MAGALHAES</t>
+  </si>
+  <si>
+    <t>de Araujo Chaves,Jaqueline</t>
+  </si>
+  <si>
+    <t>GARANHUNS</t>
+  </si>
+  <si>
+    <t>UBERABA</t>
+  </si>
+  <si>
+    <t>SILVA,FERNANDO SEIXLACK</t>
+  </si>
+  <si>
+    <t>PARAUAPEBAS</t>
+  </si>
+  <si>
+    <t>Duarte,Patricia</t>
+  </si>
+  <si>
+    <t>VIEIRA,TYCIANA</t>
+  </si>
+  <si>
+    <t>Ponta Grossa</t>
+  </si>
+  <si>
+    <t>MAGAGNIN,ALEXANDRE</t>
+  </si>
+  <si>
+    <t>GUARAPUAVA</t>
+  </si>
+  <si>
+    <t>Abdallah,Bruno</t>
+  </si>
+  <si>
+    <t>Americana</t>
+  </si>
+  <si>
+    <t>Reis Filho,Abnadar</t>
+  </si>
+  <si>
+    <t>BOTUCATU</t>
+  </si>
+  <si>
+    <t>DE ALMEIDA,DIEGO EMANUEL</t>
+  </si>
+  <si>
+    <t>Pedro,Joao and Marcilio Menezes</t>
+  </si>
+  <si>
+    <t>Passo Fundo</t>
+  </si>
+  <si>
+    <t>CAMARA,DAIANE</t>
+  </si>
+  <si>
+    <t>NATAL, RN</t>
+  </si>
+  <si>
+    <t>ITUIUTABA</t>
+  </si>
+  <si>
+    <t>Mamede Marquez,Carlos</t>
+  </si>
+  <si>
+    <t>Cachoeiro de Itapemirim</t>
+  </si>
+  <si>
     <t>DURANTE,DANIEL BARROS and DANIELA PIMENTEL MOREIRA</t>
   </si>
   <si>
-    <t>Guarujá</t>
-  </si>
-  <si>
-    <t>MANAUS</t>
-  </si>
-  <si>
-    <t>BRASILIA</t>
-  </si>
-  <si>
-    <t>Risuenho,Igor and Vinicius Costa</t>
-  </si>
-  <si>
-    <t>Canoas</t>
-  </si>
-  <si>
-    <t>Guarulhos</t>
-  </si>
-  <si>
-    <t>RYNALDO CALSAVARA,ANDRE</t>
-  </si>
-  <si>
-    <t>PETROLINA</t>
-  </si>
-  <si>
-    <t>Coelho,Caio Bezerra de Souza</t>
-  </si>
-  <si>
-    <t>TAGUATINGA</t>
-  </si>
-  <si>
-    <t>MONTES CLAROS</t>
-  </si>
-  <si>
-    <t>MARTINS,RODRIGO LUIS and WILSON ATHAYDE RIBEIRO</t>
-  </si>
-  <si>
-    <t>FORTALEZA</t>
-  </si>
-  <si>
-    <t>VARGINHA</t>
-  </si>
-  <si>
-    <t>Poloni,Gabriel Godoy</t>
-  </si>
-  <si>
-    <t>ARMACAO DOS BUZIOS</t>
-  </si>
-  <si>
-    <t>DE ALMEIDA,MATHEUS OLIVEIRA</t>
-  </si>
-  <si>
-    <t>LUIS EDUARDO MAGALHAES</t>
-  </si>
-  <si>
-    <t>de Araujo Chaves,Jaqueline</t>
-  </si>
-  <si>
-    <t>GARANHUNS</t>
-  </si>
-  <si>
-    <t>UBERABA</t>
-  </si>
-  <si>
-    <t>SILVA,FERNANDO SEIXLACK</t>
-  </si>
-  <si>
-    <t>PARAUAPEBAS</t>
-  </si>
-  <si>
-    <t>Duarte,Patricia</t>
-  </si>
-  <si>
-    <t>VIEIRA,TYCIANA</t>
-  </si>
-  <si>
-    <t>Ponta Grossa</t>
-  </si>
-  <si>
-    <t>MAGAGNIN,ALEXANDRE</t>
-  </si>
-  <si>
-    <t>GUARAPUAVA</t>
-  </si>
-  <si>
-    <t>Abdallah,Bruno</t>
-  </si>
-  <si>
-    <t>Americana</t>
-  </si>
-  <si>
-    <t>Reis Filho,Abnadar</t>
-  </si>
-  <si>
-    <t>BOTUCATU</t>
-  </si>
-  <si>
-    <t>DE ALMEIDA,DIEGO EMANUEL</t>
-  </si>
-  <si>
-    <t>Pedro,Joao and Marcilio Menezes</t>
-  </si>
-  <si>
-    <t>Passo Fundo</t>
-  </si>
-  <si>
-    <t>CAMARA,DAIANE</t>
-  </si>
-  <si>
-    <t>NATAL, RN</t>
-  </si>
-  <si>
-    <t>ITUIUTABA</t>
-  </si>
-  <si>
-    <t>Mamede Marquez,Carlos</t>
-  </si>
-  <si>
-    <t>Cachoeiro de Itapemirim</t>
-  </si>
-  <si>
     <t>AP</t>
   </si>
   <si>
@@ -908,91 +911,94 @@
     <t>187</t>
   </si>
   <si>
-    <t>121</t>
-  </si>
-  <si>
-    <t>R$ 42.334,49</t>
-  </si>
-  <si>
-    <t>448.4</t>
-  </si>
-  <si>
-    <t>273.9</t>
-  </si>
-  <si>
-    <t>5.76</t>
-  </si>
-  <si>
-    <t>19.8</t>
+    <t>80</t>
+  </si>
+  <si>
+    <t>R$ 37.922,44</t>
+  </si>
+  <si>
+    <t>455.7</t>
+  </si>
+  <si>
+    <t>279.5</t>
+  </si>
+  <si>
+    <t>5.84</t>
+  </si>
+  <si>
+    <t>20.0</t>
   </si>
   <si>
     <t>7.4</t>
   </si>
   <si>
-    <t>6.7</t>
-  </si>
-  <si>
-    <t>37.4%</t>
-  </si>
-  <si>
-    <t>19.1%</t>
+    <t>6.8</t>
+  </si>
+  <si>
+    <t>36.8%</t>
+  </si>
+  <si>
+    <t>18.9%</t>
   </si>
   <si>
     <t>2.2%</t>
   </si>
   <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>5.3%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
+  </si>
+  <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>5.5%</t>
-  </si>
-  <si>
-    <t>1.3%</t>
-  </si>
-  <si>
-    <t>6.8%</t>
-  </si>
-  <si>
-    <t>2.8%</t>
-  </si>
-  <si>
-    <t>4.3%</t>
-  </si>
-  <si>
-    <t>11118.0</t>
-  </si>
-  <si>
-    <t>9056.0</t>
-  </si>
-  <si>
-    <t>1033.0</t>
-  </si>
-  <si>
-    <t>117.0</t>
-  </si>
-  <si>
-    <t>2590.0</t>
-  </si>
-  <si>
-    <t>598.0</t>
-  </si>
-  <si>
-    <t>99.0</t>
-  </si>
-  <si>
-    <t>3214.0</t>
-  </si>
-  <si>
-    <t>1312.0</t>
-  </si>
-  <si>
-    <t>2019.0</t>
+    <t>6.7%</t>
+  </si>
+  <si>
+    <t>2.7%</t>
+  </si>
+  <si>
+    <t>4.2%</t>
+  </si>
+  <si>
+    <t>11361.0</t>
+  </si>
+  <si>
+    <t>9274.0</t>
+  </si>
+  <si>
+    <t>1083.0</t>
+  </si>
+  <si>
+    <t>128.0</t>
+  </si>
+  <si>
+    <t>2624.0</t>
+  </si>
+  <si>
+    <t>607.0</t>
+  </si>
+  <si>
+    <t>102.0</t>
+  </si>
+  <si>
+    <t>3275.0</t>
+  </si>
+  <si>
+    <t>1332.0</t>
+  </si>
+  <si>
+    <t>2077.0</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>253.0</t>
+    <t>261.0</t>
   </si>
   <si>
     <t>1</t>
@@ -1399,7 +1405,7 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="5.43" customWidth="1"/>
-    <col min="2" max="2" width="3.57" customWidth="1"/>
+    <col min="2" max="2" width="3.14" customWidth="1"/>
     <col min="3" max="3" width="17.86" customWidth="1"/>
     <col min="4" max="4" width="4.43" customWidth="1"/>
     <col min="5" max="5" width="26.57" customWidth="1"/>
@@ -1648,7 +1654,7 @@
       </c>
       <c r="L2" s="4"/>
       <c r="M2" s="5">
-        <v>55740.789999999994</v>
+        <v>49515.610000000001</v>
       </c>
       <c r="N2" s="6">
         <v>588</v>
@@ -1803,7 +1809,7 @@
       </c>
       <c r="L3" s="4"/>
       <c r="M3" s="5">
-        <v>67474.380000000005</v>
+        <v>63405.629999999997</v>
       </c>
       <c r="N3" s="6">
         <v>661</v>
@@ -1960,7 +1966,7 @@
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="5">
-        <v>57032.650000000001</v>
+        <v>51692.659999999996</v>
       </c>
       <c r="N4" s="6">
         <v>596</v>
@@ -2117,7 +2123,7 @@
       </c>
       <c r="L5" s="4"/>
       <c r="M5" s="5">
-        <v>26095.079999999998</v>
+        <v>23112.32</v>
       </c>
       <c r="N5" s="6">
         <v>276</v>
@@ -2274,7 +2280,7 @@
       </c>
       <c r="L6" s="4"/>
       <c r="M6" s="5">
-        <v>73769.509999999995</v>
+        <v>67389.539999999994</v>
       </c>
       <c r="N6" s="6">
         <v>743</v>
@@ -2431,7 +2437,7 @@
       </c>
       <c r="L7" s="4"/>
       <c r="M7" s="5">
-        <v>67124.699999999997</v>
+        <v>59184.059999999998</v>
       </c>
       <c r="N7" s="6">
         <v>673</v>
@@ -2588,7 +2594,7 @@
       </c>
       <c r="L8" s="4"/>
       <c r="M8" s="5">
-        <v>42701.629999999997</v>
+        <v>38382.400000000001</v>
       </c>
       <c r="N8" s="6">
         <v>501</v>
@@ -2745,7 +2751,7 @@
       </c>
       <c r="L9" s="4"/>
       <c r="M9" s="5">
-        <v>85751.160000000003</v>
+        <v>80691.479999999996</v>
       </c>
       <c r="N9" s="6">
         <v>833</v>
@@ -2902,7 +2908,7 @@
       </c>
       <c r="L10" s="4"/>
       <c r="M10" s="5">
-        <v>56527.809999999998</v>
+        <v>50295.730000000003</v>
       </c>
       <c r="N10" s="6">
         <v>581</v>
@@ -3059,7 +3065,7 @@
       </c>
       <c r="L11" s="4"/>
       <c r="M11" s="5">
-        <v>105959.95000000003</v>
+        <v>99277.199999999997</v>
       </c>
       <c r="N11" s="6">
         <v>1130</v>
@@ -3185,7 +3191,7 @@
         <v>19536</v>
       </c>
       <c r="B12" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c t="s" r="C12" s="4">
         <v>51</v>
@@ -3215,35 +3221,93 @@
         <v>58</v>
       </c>
       <c r="L12" s="4"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="6"/>
-      <c r="O12" s="6"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
-      <c r="AB12" s="9"/>
-      <c r="AC12" s="9"/>
-      <c r="AD12" s="6"/>
-      <c r="AE12" s="6"/>
-      <c r="AF12" s="6"/>
-      <c r="AG12" s="6"/>
-      <c r="AH12" s="6"/>
-      <c r="AI12" s="6"/>
-      <c r="AJ12" s="6"/>
-      <c r="AK12" s="6"/>
-      <c r="AL12" s="6"/>
-      <c r="AM12" s="6"/>
-      <c r="AN12" s="9"/>
-      <c r="AO12" s="6"/>
+      <c r="M12" s="5">
+        <v>44517.360000000001</v>
+      </c>
+      <c r="N12" s="6">
+        <v>583</v>
+      </c>
+      <c r="O12" s="6">
+        <v>441</v>
+      </c>
+      <c r="P12" s="7">
+        <v>5.2619891651865007</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>23.919123129251702</v>
+      </c>
+      <c r="R12" s="8">
+        <v>11.559377448747153</v>
+      </c>
+      <c r="S12" s="8">
+        <v>7</v>
+      </c>
+      <c r="T12" s="9">
+        <v>0.20634920634920634</v>
+      </c>
+      <c r="U12" s="9">
+        <v>0.099773242630385492</v>
+      </c>
+      <c r="V12" s="9">
+        <v>0.038548752834467119</v>
+      </c>
+      <c r="W12" s="9">
+        <v>0</v>
+      </c>
+      <c r="X12" s="9">
+        <v>0.020408163265306121</v>
+      </c>
+      <c r="Y12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="9">
+        <v>0.0045351473922902496</v>
+      </c>
+      <c r="AA12" s="9">
+        <v>0.0090702947845804991</v>
+      </c>
+      <c r="AB12" s="9">
+        <v>0.018140589569160998</v>
+      </c>
+      <c r="AC12" s="9">
+        <v>0.013605442176870748</v>
+      </c>
+      <c r="AD12" s="6">
+        <v>49</v>
+      </c>
+      <c r="AE12" s="6">
+        <v>44</v>
+      </c>
+      <c r="AF12" s="6">
+        <v>17</v>
+      </c>
+      <c r="AG12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="6">
+        <v>9</v>
+      </c>
+      <c r="AI12" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="6">
+        <v>2</v>
+      </c>
+      <c r="AK12" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL12" s="6">
+        <v>8</v>
+      </c>
+      <c r="AM12" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN12" s="9">
+        <v>0.0068027210884353739</v>
+      </c>
+      <c r="AO12" s="6">
+        <v>3</v>
+      </c>
       <c t="s" r="AP12" s="4">
         <v>58</v>
       </c>
@@ -3315,7 +3379,7 @@
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="5">
-        <v>70150.400000000009</v>
+        <v>61919.010000000002</v>
       </c>
       <c r="N13" s="6">
         <v>698</v>
@@ -3472,7 +3536,7 @@
       </c>
       <c r="L14" s="4"/>
       <c r="M14" s="5">
-        <v>84502.369999999995</v>
+        <v>81451.949999999997</v>
       </c>
       <c r="N14" s="6">
         <v>926</v>
@@ -3629,7 +3693,7 @@
       </c>
       <c r="L15" s="4"/>
       <c r="M15" s="5">
-        <v>37865.790000000001</v>
+        <v>33703.839999999997</v>
       </c>
       <c r="N15" s="6">
         <v>386</v>
@@ -3786,7 +3850,7 @@
       </c>
       <c r="L16" s="4"/>
       <c r="M16" s="5">
-        <v>45140.139999999999</v>
+        <v>40524.370000000003</v>
       </c>
       <c r="N16" s="6">
         <v>493</v>
@@ -3943,7 +4007,7 @@
       </c>
       <c r="L17" s="4"/>
       <c r="M17" s="5">
-        <v>36473.979999999996</v>
+        <v>32871.540000000001</v>
       </c>
       <c r="N17" s="6">
         <v>426</v>
@@ -4100,7 +4164,7 @@
       </c>
       <c r="L18" s="4"/>
       <c r="M18" s="5">
-        <v>38828.729999999996</v>
+        <v>32929.989999999998</v>
       </c>
       <c r="N18" s="6">
         <v>367</v>
@@ -4257,7 +4321,7 @@
       </c>
       <c r="L19" s="4"/>
       <c r="M19" s="5">
-        <v>61274.810000000005</v>
+        <v>52867.900000000001</v>
       </c>
       <c r="N19" s="6">
         <v>556</v>
@@ -4414,7 +4478,7 @@
       </c>
       <c r="L20" s="4"/>
       <c r="M20" s="5">
-        <v>92535.699999999997</v>
+        <v>76332.029999999999</v>
       </c>
       <c r="N20" s="6">
         <v>960</v>
@@ -4569,7 +4633,7 @@
       </c>
       <c r="L21" s="4"/>
       <c r="M21" s="5">
-        <v>59362</v>
+        <v>50201.840000000004</v>
       </c>
       <c r="N21" s="6">
         <v>544</v>
@@ -4726,7 +4790,7 @@
       </c>
       <c r="L22" s="4"/>
       <c r="M22" s="5">
-        <v>58474.400000000001</v>
+        <v>51152.139999999999</v>
       </c>
       <c r="N22" s="6">
         <v>622</v>
@@ -4883,7 +4947,7 @@
       </c>
       <c r="L23" s="4"/>
       <c r="M23" s="5">
-        <v>31342.619999999999</v>
+        <v>28427.630000000001</v>
       </c>
       <c r="N23" s="6">
         <v>355</v>
@@ -5040,7 +5104,7 @@
       </c>
       <c r="L24" s="4"/>
       <c r="M24" s="5">
-        <v>53742.440000000002</v>
+        <v>47774.139999999999</v>
       </c>
       <c r="N24" s="6">
         <v>591</v>
@@ -5197,7 +5261,7 @@
       </c>
       <c r="L25" s="4"/>
       <c r="M25" s="5">
-        <v>93185.449999999997</v>
+        <v>83823.910000000003</v>
       </c>
       <c r="N25" s="6">
         <v>1179</v>
@@ -5354,7 +5418,7 @@
       </c>
       <c r="L26" s="4"/>
       <c r="M26" s="5">
-        <v>37562.809999999998</v>
+        <v>33645.510000000002</v>
       </c>
       <c r="N26" s="6">
         <v>425</v>
@@ -5480,7 +5544,7 @@
         <v>19579</v>
       </c>
       <c r="B27" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>51</v>
@@ -5511,82 +5575,82 @@
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="5">
-        <v>23608.759999999998</v>
+        <v>36955.860000000001</v>
       </c>
       <c r="N27" s="6">
-        <v>115</v>
+        <v>420</v>
       </c>
       <c r="O27" s="6">
-        <v>67</v>
+        <v>282</v>
       </c>
       <c r="P27" s="7">
-        <v>5.0342342342342334</v>
+        <v>5.9843723192019951</v>
       </c>
       <c r="Q27" s="8">
-        <v>17.01044776119403</v>
+        <v>19.854905319148937</v>
       </c>
       <c r="R27" s="8">
-        <v>4.798010447761194</v>
+        <v>6.5442264285714282</v>
       </c>
       <c r="S27" s="8">
         <v>7</v>
       </c>
       <c r="T27" s="9">
-        <v>0.52238805970149249</v>
+        <v>0.29432624113475175</v>
       </c>
       <c r="U27" s="9">
-        <v>0.059701492537313432</v>
+        <v>0.046099290780141841</v>
       </c>
       <c r="V27" s="9">
-        <v>0.014925373134328358</v>
+        <v>0.014184397163120567</v>
       </c>
       <c r="W27" s="9">
         <v>0</v>
       </c>
       <c r="X27" s="9">
-        <v>0.044776119402985072</v>
+        <v>0.028368794326241134</v>
       </c>
       <c r="Y27" s="9">
-        <v>0</v>
+        <v>0.0035460992907801418</v>
       </c>
       <c r="Z27" s="9">
         <v>0</v>
       </c>
       <c r="AA27" s="9">
-        <v>0.014925373134328358</v>
+        <v>0.014184397163120567</v>
       </c>
       <c r="AB27" s="9">
-        <v>0</v>
+        <v>0.0035460992907801418</v>
       </c>
       <c r="AC27" s="9">
-        <v>0.029850746268656716</v>
+        <v>0.0070921985815602835</v>
       </c>
       <c r="AD27" s="6">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AE27" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF27" s="6">
         <v>4</v>
       </c>
-      <c r="AF27" s="6">
-        <v>1</v>
-      </c>
       <c r="AG27" s="6">
         <v>0</v>
       </c>
       <c r="AH27" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AI27" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ27" s="6">
         <v>0</v>
       </c>
       <c r="AK27" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL27" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM27" s="6">
         <v>2</v>
@@ -5668,7 +5732,7 @@
       </c>
       <c r="L28" s="4"/>
       <c r="M28" s="5">
-        <v>44431.940000000002</v>
+        <v>42245.879999999997</v>
       </c>
       <c r="N28" s="6">
         <v>435</v>
@@ -5825,7 +5889,7 @@
       </c>
       <c r="L29" s="4"/>
       <c r="M29" s="5">
-        <v>54526.700000000004</v>
+        <v>51843.980000000003</v>
       </c>
       <c r="N29" s="6">
         <v>539</v>
@@ -5982,7 +6046,7 @@
       </c>
       <c r="L30" s="4"/>
       <c r="M30" s="5">
-        <v>81625.360000000001</v>
+        <v>73127.520000000004</v>
       </c>
       <c r="N30" s="6">
         <v>809</v>
@@ -6137,7 +6201,7 @@
       </c>
       <c r="L31" s="4"/>
       <c r="M31" s="5">
-        <v>48944.869999999995</v>
+        <v>43431.970000000008</v>
       </c>
       <c r="N31" s="6">
         <v>537</v>
@@ -6294,7 +6358,7 @@
       </c>
       <c r="L32" s="4"/>
       <c r="M32" s="5">
-        <v>65975.369999999995</v>
+        <v>58329.919999999998</v>
       </c>
       <c r="N32" s="6">
         <v>737</v>
@@ -6449,7 +6513,7 @@
       </c>
       <c r="L33" s="4"/>
       <c r="M33" s="5">
-        <v>53705.309999999998</v>
+        <v>47911.220000000008</v>
       </c>
       <c r="N33" s="6">
         <v>617</v>
@@ -6604,7 +6668,7 @@
       </c>
       <c r="L34" s="4"/>
       <c r="M34" s="5">
-        <v>45022.970000000008</v>
+        <v>42897.879999999997</v>
       </c>
       <c r="N34" s="6">
         <v>534</v>
@@ -6761,7 +6825,7 @@
       </c>
       <c r="L35" s="4"/>
       <c r="M35" s="5">
-        <v>51976.509999999995</v>
+        <v>46250.830000000002</v>
       </c>
       <c r="N35" s="6">
         <v>577</v>
@@ -6887,7 +6951,7 @@
         <v>19602</v>
       </c>
       <c r="B36" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6917,35 +6981,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>6079.0600000000004</v>
+      </c>
+      <c r="N36" s="6">
+        <v>70</v>
+      </c>
+      <c r="O36" s="6">
+        <v>35</v>
+      </c>
+      <c r="P36" s="7">
+        <v>6.2978571428571435</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>28.357617142857144</v>
+      </c>
+      <c r="R36" s="8">
+        <v>14.746665714285713</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.085714285714285715</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.085714285714285715</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0.057142857142857141</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -7017,7 +7139,7 @@
       </c>
       <c r="L37" s="4"/>
       <c r="M37" s="5">
-        <v>14335.289999999999</v>
+        <v>12731.75</v>
       </c>
       <c r="N37" s="6">
         <v>158</v>
@@ -7172,7 +7294,7 @@
       </c>
       <c r="L38" s="4"/>
       <c r="M38" s="5">
-        <v>36651.300000000003</v>
+        <v>34664.800000000003</v>
       </c>
       <c r="N38" s="6">
         <v>422</v>
@@ -7329,7 +7451,7 @@
       </c>
       <c r="L39" s="4"/>
       <c r="M39" s="5">
-        <v>36712.830000000002</v>
+        <v>32971.400000000001</v>
       </c>
       <c r="N39" s="6">
         <v>419</v>
@@ -7486,7 +7608,7 @@
       </c>
       <c r="L40" s="4"/>
       <c r="M40" s="5">
-        <v>45697.510000000002</v>
+        <v>40607.610000000001</v>
       </c>
       <c r="N40" s="6">
         <v>551</v>
@@ -7641,7 +7763,7 @@
       </c>
       <c r="L41" s="4"/>
       <c r="M41" s="5">
-        <v>60922.710000000006</v>
+        <v>55689.099999999999</v>
       </c>
       <c r="N41" s="6">
         <v>668</v>
@@ -7798,7 +7920,7 @@
       </c>
       <c r="L42" s="4"/>
       <c r="M42" s="5">
-        <v>70852.279999999999</v>
+        <v>61599.889999999999</v>
       </c>
       <c r="N42" s="6">
         <v>737</v>
@@ -7924,7 +8046,7 @@
         <v>19618</v>
       </c>
       <c r="B43" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c t="s" r="C43" s="4">
         <v>51</v>
@@ -7954,35 +8076,93 @@
         <v>58</v>
       </c>
       <c r="L43" s="4"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="6"/>
-      <c r="P43" s="7"/>
-      <c r="Q43" s="8"/>
-      <c r="R43" s="8"/>
-      <c r="S43" s="8"/>
-      <c r="T43" s="9"/>
-      <c r="U43" s="9"/>
-      <c r="V43" s="9"/>
-      <c r="W43" s="9"/>
-      <c r="X43" s="9"/>
-      <c r="Y43" s="9"/>
-      <c r="Z43" s="9"/>
-      <c r="AA43" s="9"/>
-      <c r="AB43" s="9"/>
-      <c r="AC43" s="9"/>
-      <c r="AD43" s="6"/>
-      <c r="AE43" s="6"/>
-      <c r="AF43" s="6"/>
-      <c r="AG43" s="6"/>
-      <c r="AH43" s="6"/>
-      <c r="AI43" s="6"/>
-      <c r="AJ43" s="6"/>
-      <c r="AK43" s="6"/>
-      <c r="AL43" s="6"/>
-      <c r="AM43" s="6"/>
-      <c r="AN43" s="9"/>
-      <c r="AO43" s="6"/>
+      <c r="M43" s="5">
+        <v>52837.199999999997</v>
+      </c>
+      <c r="N43" s="6">
+        <v>672</v>
+      </c>
+      <c r="O43" s="6">
+        <v>511</v>
+      </c>
+      <c r="P43" s="7">
+        <v>9.1141006220839813</v>
+      </c>
+      <c r="Q43" s="8">
+        <v>23.779582387475536</v>
+      </c>
+      <c r="R43" s="8">
+        <v>7.2484427435387673</v>
+      </c>
+      <c r="S43" s="8">
+        <v>7</v>
+      </c>
+      <c r="T43" s="9">
+        <v>0.25636007827788648</v>
+      </c>
+      <c r="U43" s="9">
+        <v>0.16046966731898238</v>
+      </c>
+      <c r="V43" s="9">
+        <v>0.037181996086105673</v>
+      </c>
+      <c r="W43" s="9">
+        <v>0.0097847358119999995</v>
+      </c>
+      <c r="X43" s="9">
+        <v>0.013698630136986301</v>
+      </c>
+      <c r="Y43" s="9">
+        <v>0.0019569471624266144</v>
+      </c>
+      <c r="Z43" s="9">
+        <v>0.0019569471624266144</v>
+      </c>
+      <c r="AA43" s="9">
+        <v>0.023483365949119372</v>
+      </c>
+      <c r="AB43" s="9">
+        <v>0.0097847358121330719</v>
+      </c>
+      <c r="AC43" s="9">
+        <v>0.074363992172211346</v>
+      </c>
+      <c r="AD43" s="6">
+        <v>87</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>82</v>
+      </c>
+      <c r="AF43" s="6">
+        <v>19</v>
+      </c>
+      <c r="AG43" s="6">
+        <v>5</v>
+      </c>
+      <c r="AH43" s="6">
+        <v>7</v>
+      </c>
+      <c r="AI43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK43" s="6">
+        <v>12</v>
+      </c>
+      <c r="AL43" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM43" s="6">
+        <v>38</v>
+      </c>
+      <c r="AN43" s="9">
+        <v>0.0078277886497064575</v>
+      </c>
+      <c r="AO43" s="6">
+        <v>4</v>
+      </c>
       <c t="s" r="AP43" s="4">
         <v>58</v>
       </c>
@@ -8054,7 +8234,7 @@
       </c>
       <c r="L44" s="4"/>
       <c r="M44" s="5">
-        <v>49410.950000000004</v>
+        <v>44391.18</v>
       </c>
       <c r="N44" s="6">
         <v>552</v>
@@ -8211,7 +8391,7 @@
       </c>
       <c r="L45" s="4"/>
       <c r="M45" s="5">
-        <v>31487.409999999996</v>
+        <v>28541.02</v>
       </c>
       <c r="N45" s="6">
         <v>361</v>
@@ -8366,7 +8546,7 @@
       </c>
       <c r="L46" s="4"/>
       <c r="M46" s="5">
-        <v>28066.539999999997</v>
+        <v>25469.700000000001</v>
       </c>
       <c r="N46" s="6">
         <v>331</v>
@@ -8521,7 +8701,7 @@
       </c>
       <c r="L47" s="4"/>
       <c r="M47" s="5">
-        <v>53289.279999999992</v>
+        <v>50241.110000000001</v>
       </c>
       <c r="N47" s="6">
         <v>522</v>
@@ -8678,7 +8858,7 @@
       </c>
       <c r="L48" s="4"/>
       <c r="M48" s="5">
-        <v>53554.199999999997</v>
+        <v>43201.970000000008</v>
       </c>
       <c r="N48" s="6">
         <v>603</v>
@@ -8833,7 +9013,7 @@
       </c>
       <c r="L49" s="4"/>
       <c r="M49" s="5">
-        <v>40070.079999999994</v>
+        <v>36041.879999999997</v>
       </c>
       <c r="N49" s="6">
         <v>449</v>
@@ -8989,7 +9169,9 @@
         <v>58</v>
       </c>
       <c r="L50" s="4"/>
-      <c r="M50" s="5"/>
+      <c r="M50" s="5">
+        <v>22836.049999999999</v>
+      </c>
       <c r="N50" s="6"/>
       <c r="O50" s="6"/>
       <c r="P50" s="7"/>
@@ -9089,7 +9271,7 @@
       </c>
       <c r="L51" s="4"/>
       <c r="M51" s="5">
-        <v>50504.62999999999</v>
+        <v>45148.440000000002</v>
       </c>
       <c r="N51" s="6">
         <v>582</v>
@@ -9215,7 +9397,7 @@
         <v>19642</v>
       </c>
       <c r="B52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C52" s="4">
         <v>51</v>
@@ -9246,40 +9428,40 @@
       </c>
       <c r="L52" s="4"/>
       <c r="M52" s="5">
-        <v>23461.235000000001</v>
+        <v>26031.099999999999</v>
       </c>
       <c r="N52" s="6">
-        <v>240</v>
+        <v>327</v>
       </c>
       <c r="O52" s="6">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="P52" s="7">
-        <v>4.0774999999999997</v>
+        <v>4.76518868501529</v>
       </c>
       <c r="Q52" s="8">
-        <v>15.89223893129771</v>
+        <v>16.923172727272728</v>
       </c>
       <c r="R52" s="8">
-        <v>4.5287526717557256</v>
+        <v>4.8053758064516128</v>
       </c>
       <c r="S52" s="8">
         <v>7</v>
       </c>
       <c r="T52" s="9">
-        <v>0.51908396946564883</v>
+        <v>0.44919786096256686</v>
       </c>
       <c r="U52" s="9">
-        <v>0.061068702290076333</v>
+        <v>0.085561497326203204</v>
       </c>
       <c r="V52" s="9">
-        <v>0.022900763358778626</v>
+        <v>0.021390374331550801</v>
       </c>
       <c r="W52" s="9">
         <v>0</v>
       </c>
       <c r="X52" s="9">
-        <v>0.022900763358778626</v>
+        <v>0.016042780748663103</v>
       </c>
       <c r="Y52" s="9">
         <v>0</v>
@@ -9288,22 +9470,22 @@
         <v>0</v>
       </c>
       <c r="AA52" s="9">
-        <v>0</v>
+        <v>0.0053475935828877002</v>
       </c>
       <c r="AB52" s="9">
-        <v>0</v>
+        <v>0.0106951871657754</v>
       </c>
       <c r="AC52" s="9">
-        <v>0.015267175572519083</v>
+        <v>0.032085561497326207</v>
       </c>
       <c r="AD52" s="6">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AE52" s="6">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AF52" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG52" s="6">
         <v>0</v>
@@ -9318,13 +9500,13 @@
         <v>0</v>
       </c>
       <c r="AK52" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL52" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM52" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AN52" s="9">
         <v>0</v>
@@ -9401,7 +9583,7 @@
       </c>
       <c r="L53" s="4"/>
       <c r="M53" s="5">
-        <v>33502.190000000002</v>
+        <v>29900.939999999999</v>
       </c>
       <c r="N53" s="6">
         <v>350</v>
@@ -9558,7 +9740,7 @@
       </c>
       <c r="L54" s="4"/>
       <c r="M54" s="5">
-        <v>38383.399999999987</v>
+        <v>34712.220000000001</v>
       </c>
       <c r="N54" s="6">
         <v>429</v>
@@ -9713,7 +9895,7 @@
       </c>
       <c r="L55" s="4"/>
       <c r="M55" s="5">
-        <v>55698.099999999999</v>
+        <v>49419.550000000003</v>
       </c>
       <c r="N55" s="6">
         <v>624</v>
@@ -9868,7 +10050,7 @@
       </c>
       <c r="L56" s="4"/>
       <c r="M56" s="5">
-        <v>97997.449999999983</v>
+        <v>86670.139999999999</v>
       </c>
       <c r="N56" s="6">
         <v>986</v>
@@ -10023,7 +10205,7 @@
       </c>
       <c r="L57" s="4"/>
       <c r="M57" s="5">
-        <v>38354.859999999993</v>
+        <v>34200.25</v>
       </c>
       <c r="N57" s="6">
         <v>462</v>
@@ -10177,7 +10359,9 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
+      <c r="M58" s="5">
+        <v>16826.759999999998</v>
+      </c>
       <c r="N58" s="6"/>
       <c r="O58" s="6"/>
       <c r="P58" s="7"/>
@@ -10277,7 +10461,7 @@
       </c>
       <c r="L59" s="4"/>
       <c r="M59" s="5">
-        <v>37571.270000000004</v>
+        <v>33893.699999999997</v>
       </c>
       <c r="N59" s="6">
         <v>390</v>
@@ -10432,7 +10616,7 @@
       </c>
       <c r="L60" s="4"/>
       <c r="M60" s="5">
-        <v>55544.770000000004</v>
+        <v>49359.809999999998</v>
       </c>
       <c r="N60" s="6">
         <v>631</v>
@@ -10587,7 +10771,7 @@
       </c>
       <c r="L61" s="4"/>
       <c r="M61" s="5">
-        <v>55279.610000000001</v>
+        <v>46606.230000000003</v>
       </c>
       <c r="N61" s="6">
         <v>532</v>
@@ -10744,7 +10928,7 @@
       </c>
       <c r="L62" s="4"/>
       <c r="M62" s="5">
-        <v>48410</v>
+        <v>42786.389999999999</v>
       </c>
       <c r="N62" s="6">
         <v>526</v>
@@ -10899,7 +11083,7 @@
       </c>
       <c r="L63" s="4"/>
       <c r="M63" s="5">
-        <v>53105.809999999998</v>
+        <v>47500.550000000003</v>
       </c>
       <c r="N63" s="6">
         <v>564</v>
@@ -10917,7 +11101,7 @@
         <v>4.3924447802197797</v>
       </c>
       <c r="S63" s="8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T63" s="9">
         <v>0.50918635170603677</v>
@@ -11056,7 +11240,7 @@
       </c>
       <c r="L64" s="4"/>
       <c r="M64" s="5">
-        <v>12718.470000000001</v>
+        <v>11839.4</v>
       </c>
       <c r="N64" s="6">
         <v>164</v>
@@ -11213,7 +11397,7 @@
       </c>
       <c r="L65" s="4"/>
       <c r="M65" s="5">
-        <v>56592.37999999999</v>
+        <v>50631.82</v>
       </c>
       <c r="N65" s="6">
         <v>589</v>
@@ -11369,7 +11553,9 @@
         <v>58</v>
       </c>
       <c r="L66" s="4"/>
-      <c r="M66" s="5"/>
+      <c r="M66" s="5">
+        <v>29502.82</v>
+      </c>
       <c r="N66" s="6"/>
       <c r="O66" s="6"/>
       <c r="P66" s="7"/>
@@ -11469,7 +11655,7 @@
       </c>
       <c r="L67" s="4"/>
       <c r="M67" s="5">
-        <v>26353.790000000001</v>
+        <v>23716.23</v>
       </c>
       <c r="N67" s="6">
         <v>292</v>
@@ -11626,7 +11812,7 @@
       </c>
       <c r="L68" s="4"/>
       <c r="M68" s="5">
-        <v>34514.839999999997</v>
+        <v>31730.639999999996</v>
       </c>
       <c r="N68" s="6">
         <v>446</v>
@@ -11783,7 +11969,7 @@
       </c>
       <c r="L69" s="4"/>
       <c r="M69" s="5">
-        <v>30691.200000000004</v>
+        <v>28426.18</v>
       </c>
       <c r="N69" s="6">
         <v>347</v>
@@ -11940,7 +12126,7 @@
       </c>
       <c r="L70" s="4"/>
       <c r="M70" s="5">
-        <v>44123.419999999998</v>
+        <v>41386.449999999997</v>
       </c>
       <c r="N70" s="6">
         <v>416</v>
@@ -12095,7 +12281,7 @@
       </c>
       <c r="L71" s="4"/>
       <c r="M71" s="5">
-        <v>60353.120000000003</v>
+        <v>50782.830000000002</v>
       </c>
       <c r="N71" s="6">
         <v>555</v>
@@ -12221,7 +12407,7 @@
         <v>19693</v>
       </c>
       <c r="B72" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c t="s" r="C72" s="4">
         <v>51</v>
@@ -12250,82 +12436,82 @@
       </c>
       <c r="L72" s="4"/>
       <c r="M72" s="5">
-        <v>23299.710000000003</v>
+        <v>43046.470000000008</v>
       </c>
       <c r="N72" s="6">
-        <v>39</v>
+        <v>486</v>
       </c>
       <c r="O72" s="6">
-        <v>24</v>
+        <v>259</v>
       </c>
       <c r="P72" s="7">
-        <v>4.4210526315789478</v>
+        <v>5.9947786307053939</v>
       </c>
       <c r="Q72" s="8">
-        <v>19.111804166666666</v>
+        <v>25.467631274131275</v>
       </c>
       <c r="R72" s="8">
-        <v>8.2015136363636358</v>
+        <v>12.096082071713147</v>
       </c>
       <c r="S72" s="8">
         <v>8.3000000000000007</v>
       </c>
       <c r="T72" s="9">
-        <v>0.20833333333333334</v>
+        <v>0.14671814671814673</v>
       </c>
       <c r="U72" s="9">
-        <v>0.125</v>
+        <v>0.084942084942084939</v>
       </c>
       <c r="V72" s="9">
-        <v>0.041666666666666664</v>
+        <v>0.030888030888030889</v>
       </c>
       <c r="W72" s="9">
-        <v>0.041666666666000003</v>
+        <v>0.019305019305000001</v>
       </c>
       <c r="X72" s="9">
-        <v>0.041666666666666664</v>
+        <v>0.027027027027027029</v>
       </c>
       <c r="Y72" s="9">
-        <v>0.083333333333333329</v>
+        <v>0.027027027027027029</v>
       </c>
       <c r="Z72" s="9">
         <v>0</v>
       </c>
       <c r="AA72" s="9">
-        <v>0.083333333333333329</v>
+        <v>0.030888030888030889</v>
       </c>
       <c r="AB72" s="9">
-        <v>0.041666666666666664</v>
+        <v>0.011583011583011582</v>
       </c>
       <c r="AC72" s="9">
         <v>0</v>
       </c>
       <c r="AD72" s="6">
+        <v>33</v>
+      </c>
+      <c r="AE72" s="6">
+        <v>22</v>
+      </c>
+      <c r="AF72" s="6">
+        <v>8</v>
+      </c>
+      <c r="AG72" s="6">
+        <v>5</v>
+      </c>
+      <c r="AH72" s="6">
         <v>7</v>
       </c>
-      <c r="AE72" s="6">
+      <c r="AI72" s="6">
+        <v>7</v>
+      </c>
+      <c r="AJ72" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK72" s="6">
+        <v>8</v>
+      </c>
+      <c r="AL72" s="6">
         <v>3</v>
-      </c>
-      <c r="AF72" s="6">
-        <v>1</v>
-      </c>
-      <c r="AG72" s="6">
-        <v>1</v>
-      </c>
-      <c r="AH72" s="6">
-        <v>1</v>
-      </c>
-      <c r="AI72" s="6">
-        <v>2</v>
-      </c>
-      <c r="AJ72" s="6">
-        <v>0</v>
-      </c>
-      <c r="AK72" s="6">
-        <v>2</v>
-      </c>
-      <c r="AL72" s="6">
-        <v>1</v>
       </c>
       <c r="AM72" s="6">
         <v>0</v>
@@ -12407,7 +12593,7 @@
       </c>
       <c r="L73" s="4"/>
       <c r="M73" s="5">
-        <v>49657.710000000006</v>
+        <v>43558.550000000003</v>
       </c>
       <c r="N73" s="6">
         <v>499</v>
@@ -12564,7 +12750,7 @@
       </c>
       <c r="L74" s="4"/>
       <c r="M74" s="5">
-        <v>52754.050000000003</v>
+        <v>47285.059999999998</v>
       </c>
       <c r="N74" s="6">
         <v>593</v>
@@ -12721,7 +12907,7 @@
       </c>
       <c r="L75" s="4"/>
       <c r="M75" s="5">
-        <v>33136.520000000004</v>
+        <v>29519.91</v>
       </c>
       <c r="N75" s="6">
         <v>389</v>
@@ -12876,7 +13062,7 @@
       </c>
       <c r="L76" s="4"/>
       <c r="M76" s="5">
-        <v>50199.120000000003</v>
+        <v>44957.970000000008</v>
       </c>
       <c r="N76" s="6">
         <v>546</v>
@@ -13032,7 +13218,9 @@
         <v>58</v>
       </c>
       <c r="L77" s="4"/>
-      <c r="M77" s="5"/>
+      <c r="M77" s="5">
+        <v>32899.32</v>
+      </c>
       <c r="N77" s="6"/>
       <c r="O77" s="6"/>
       <c r="P77" s="7"/>
@@ -13132,7 +13320,7 @@
       </c>
       <c r="L78" s="4"/>
       <c r="M78" s="5">
-        <v>47748.430000000008</v>
+        <v>44813.239999999998</v>
       </c>
       <c r="N78" s="6">
         <v>508</v>
@@ -13289,7 +13477,7 @@
       </c>
       <c r="L79" s="4"/>
       <c r="M79" s="5">
-        <v>30552.130000000005</v>
+        <v>28899.25</v>
       </c>
       <c r="N79" s="6">
         <v>306</v>
@@ -13446,7 +13634,7 @@
       </c>
       <c r="L80" s="4"/>
       <c r="M80" s="5">
-        <v>34959.75</v>
+        <v>31557.59</v>
       </c>
       <c r="N80" s="6">
         <v>312</v>
@@ -13603,7 +13791,7 @@
       </c>
       <c r="L81" s="4"/>
       <c r="M81" s="5">
-        <v>45643.419999999998</v>
+        <v>39449.279999999992</v>
       </c>
       <c r="N81" s="6">
         <v>469</v>
@@ -13758,7 +13946,7 @@
       </c>
       <c r="L82" s="4"/>
       <c r="M82" s="5">
-        <v>31839.389999999996</v>
+        <v>28841.130000000001</v>
       </c>
       <c r="N82" s="6">
         <v>347</v>
@@ -13884,7 +14072,7 @@
         <v>19719</v>
       </c>
       <c r="B83" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c t="s" r="C83" s="4">
         <v>51</v>
@@ -13915,82 +14103,82 @@
       </c>
       <c r="L83" s="4"/>
       <c r="M83" s="5">
-        <v>20726.545000000002</v>
+        <v>27451.18</v>
       </c>
       <c r="N83" s="6">
-        <v>55</v>
+        <v>307</v>
       </c>
       <c r="O83" s="6">
-        <v>36</v>
+        <v>206</v>
       </c>
       <c r="P83" s="7">
-        <v>7.5983050847457632</v>
+        <v>13.082529581993569</v>
       </c>
       <c r="Q83" s="8">
-        <v>23.916202777777777</v>
+        <v>27.389724757281552</v>
       </c>
       <c r="R83" s="8">
-        <v>15.045833333333334</v>
+        <v>9.6988101190476197</v>
       </c>
       <c r="S83" s="8">
         <v>7</v>
       </c>
       <c r="T83" s="9">
-        <v>0.47222222222222221</v>
+        <v>0.21359223300970873</v>
       </c>
       <c r="U83" s="9">
-        <v>0.44444444444444442</v>
+        <v>0.24271844660194175</v>
       </c>
       <c r="V83" s="9">
-        <v>0</v>
+        <v>0.0048543689320388345</v>
       </c>
       <c r="W83" s="9">
-        <v>0.027777777776999999</v>
+        <v>0.0097087378640000003</v>
       </c>
       <c r="X83" s="9">
-        <v>0.027777777777777776</v>
+        <v>0.033980582524271843</v>
       </c>
       <c r="Y83" s="9">
-        <v>0.027777777777777776</v>
+        <v>0.014563106796116505</v>
       </c>
       <c r="Z83" s="9">
         <v>0</v>
       </c>
       <c r="AA83" s="9">
-        <v>0.41666666666666669</v>
+        <v>0.20873786407766989</v>
       </c>
       <c r="AB83" s="9">
-        <v>0</v>
+        <v>0.0048543689320388345</v>
       </c>
       <c r="AC83" s="9">
         <v>0</v>
       </c>
       <c r="AD83" s="6">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="AE83" s="6">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="AF83" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG83" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH83" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AI83" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ83" s="6">
         <v>0</v>
       </c>
       <c r="AK83" s="6">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="AL83" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM83" s="6">
         <v>0</v>
@@ -14072,7 +14260,7 @@
       </c>
       <c r="L84" s="4"/>
       <c r="M84" s="5">
-        <v>35768.410000000003</v>
+        <v>31430.970000000001</v>
       </c>
       <c r="N84" s="6">
         <v>360</v>
@@ -14229,7 +14417,7 @@
       </c>
       <c r="L85" s="4"/>
       <c r="M85" s="5">
-        <v>41589.400000000001</v>
+        <v>39339.409999999996</v>
       </c>
       <c r="N85" s="6">
         <v>482</v>
@@ -14384,7 +14572,7 @@
       </c>
       <c r="L86" s="4"/>
       <c r="M86" s="5">
-        <v>38238.889999999999</v>
+        <v>34632.75</v>
       </c>
       <c r="N86" s="6">
         <v>359</v>
@@ -14541,7 +14729,7 @@
       </c>
       <c r="L87" s="4"/>
       <c r="M87" s="5">
-        <v>20705.259999999998</v>
+        <v>19583.029999999999</v>
       </c>
       <c r="N87" s="6">
         <v>265</v>
@@ -14698,7 +14886,7 @@
       </c>
       <c r="L88" s="4"/>
       <c r="M88" s="5">
-        <v>33648.82</v>
+        <v>30466.84</v>
       </c>
       <c r="N88" s="6">
         <v>382</v>
@@ -14854,7 +15042,9 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
+      <c r="M89" s="5">
+        <v>82900.139999999999</v>
+      </c>
       <c r="N89" s="6"/>
       <c r="O89" s="6"/>
       <c r="P89" s="7"/>
@@ -14952,7 +15142,7 @@
       </c>
       <c r="L90" s="4"/>
       <c r="M90" s="5">
-        <v>62360.949999999997</v>
+        <v>54325.900000000001</v>
       </c>
       <c r="N90" s="6">
         <v>640</v>
@@ -15108,7 +15298,9 @@
         <v>58</v>
       </c>
       <c r="L91" s="4"/>
-      <c r="M91" s="5"/>
+      <c r="M91" s="5">
+        <v>41904.300000000003</v>
+      </c>
       <c r="N91" s="6"/>
       <c r="O91" s="6"/>
       <c r="P91" s="7"/>
@@ -15208,7 +15400,7 @@
       </c>
       <c r="L92" s="4"/>
       <c r="M92" s="5">
-        <v>14839.65</v>
+        <v>13752.16</v>
       </c>
       <c r="N92" s="6">
         <v>161</v>
@@ -15363,7 +15555,7 @@
       </c>
       <c r="L93" s="4"/>
       <c r="M93" s="5">
-        <v>54663.669999999998</v>
+        <v>48367.080000000002</v>
       </c>
       <c r="N93" s="6">
         <v>634</v>
@@ -15518,7 +15710,7 @@
       </c>
       <c r="L94" s="4"/>
       <c r="M94" s="5">
-        <v>90321.420000000013</v>
+        <v>83311.270000000004</v>
       </c>
       <c r="N94" s="6">
         <v>806</v>
@@ -15675,7 +15867,7 @@
       </c>
       <c r="L95" s="4"/>
       <c r="M95" s="5">
-        <v>53650.770000000004</v>
+        <v>47293.409999999996</v>
       </c>
       <c r="N95" s="6">
         <v>473</v>
@@ -15832,7 +16024,7 @@
       </c>
       <c r="L96" s="4"/>
       <c r="M96" s="5">
-        <v>31323.480000000003</v>
+        <v>28406.810000000001</v>
       </c>
       <c r="N96" s="6">
         <v>345</v>
@@ -15958,7 +16150,7 @@
         <v>19742</v>
       </c>
       <c r="B97" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="s" r="C97" s="4">
         <v>51</v>
@@ -15987,67 +16179,67 @@
       </c>
       <c r="L97" s="4"/>
       <c r="M97" s="5">
-        <v>18105.966666666667</v>
+        <v>28183.02</v>
       </c>
       <c r="N97" s="6">
-        <v>71</v>
+        <v>290</v>
       </c>
       <c r="O97" s="6">
-        <v>41</v>
+        <v>174</v>
       </c>
       <c r="P97" s="7">
-        <v>9.0309528571428572</v>
+        <v>10.915610211267605</v>
       </c>
       <c r="Q97" s="8">
-        <v>32.098373170731712</v>
+        <v>33.086781034482762</v>
       </c>
       <c r="R97" s="8">
-        <v>17.789473684210527</v>
+        <v>15.497006586826348</v>
       </c>
       <c r="S97" s="8">
         <v>8</v>
       </c>
       <c r="T97" s="9">
-        <v>0.26829268292682928</v>
+        <v>0.097701149425287362</v>
       </c>
       <c r="U97" s="9">
-        <v>0.29268292682926828</v>
+        <v>0.17816091954022989</v>
       </c>
       <c r="V97" s="9">
-        <v>0.073170731707317069</v>
+        <v>0.028735632183908046</v>
       </c>
       <c r="W97" s="9">
-        <v>0.024390243902000001</v>
+        <v>0.011494252873</v>
       </c>
       <c r="X97" s="9">
-        <v>0.073170731707317069</v>
+        <v>0.017241379310344827</v>
       </c>
       <c r="Y97" s="9">
-        <v>0.024390243902439025</v>
+        <v>0.0057471264367816091</v>
       </c>
       <c r="Z97" s="9">
         <v>0</v>
       </c>
       <c r="AA97" s="9">
-        <v>0.12195121951219512</v>
+        <v>0.068965517241379309</v>
       </c>
       <c r="AB97" s="9">
-        <v>0.024390243902439025</v>
+        <v>0.011494252873563218</v>
       </c>
       <c r="AC97" s="9">
-        <v>0.04878048780487805</v>
+        <v>0.057471264367816091</v>
       </c>
       <c r="AD97" s="6">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="AE97" s="6">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="AF97" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG97" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH97" s="6">
         <v>3</v>
@@ -16059,19 +16251,19 @@
         <v>0</v>
       </c>
       <c r="AK97" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AL97" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM97" s="6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AN97" s="9">
-        <v>0</v>
+        <v>0.0057471264367816091</v>
       </c>
       <c r="AO97" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="s" r="AP97" s="4">
         <v>58</v>
@@ -16144,7 +16336,7 @@
       </c>
       <c r="L98" s="4"/>
       <c r="M98" s="5">
-        <v>27781.790000000001</v>
+        <v>26133.5</v>
       </c>
       <c r="N98" s="6">
         <v>306</v>
@@ -16301,7 +16493,7 @@
       </c>
       <c r="L99" s="4"/>
       <c r="M99" s="5">
-        <v>51036.800000000003</v>
+        <v>45777.779999999992</v>
       </c>
       <c r="N99" s="6">
         <v>614</v>
@@ -16456,7 +16648,7 @@
       </c>
       <c r="L100" s="4"/>
       <c r="M100" s="5">
-        <v>31718.230000000003</v>
+        <v>28723.599999999999</v>
       </c>
       <c r="N100" s="6">
         <v>342</v>
@@ -16611,7 +16803,7 @@
       </c>
       <c r="L101" s="4"/>
       <c r="M101" s="5">
-        <v>27214.859999999997</v>
+        <v>24901.709999999999</v>
       </c>
       <c r="N101" s="6">
         <v>301</v>
@@ -16768,7 +16960,7 @@
       </c>
       <c r="L102" s="4"/>
       <c r="M102" s="5">
-        <v>45803.110000000001</v>
+        <v>40008.840000000004</v>
       </c>
       <c r="N102" s="6">
         <v>534</v>
@@ -16925,7 +17117,7 @@
       </c>
       <c r="L103" s="4"/>
       <c r="M103" s="5">
-        <v>66790.630000000005</v>
+        <v>58086.540000000001</v>
       </c>
       <c r="N103" s="6">
         <v>673</v>
@@ -17082,7 +17274,7 @@
       </c>
       <c r="L104" s="4"/>
       <c r="M104" s="5">
-        <v>15380.629999999999</v>
+        <v>14067.73</v>
       </c>
       <c r="N104" s="6">
         <v>158</v>
@@ -17239,7 +17431,7 @@
       </c>
       <c r="L105" s="4"/>
       <c r="M105" s="5">
-        <v>34228</v>
+        <v>30594.560000000001</v>
       </c>
       <c r="N105" s="6">
         <v>343</v>
@@ -17396,7 +17588,7 @@
       </c>
       <c r="L106" s="4"/>
       <c r="M106" s="5">
-        <v>19820.970000000001</v>
+        <v>24261.639999999996</v>
       </c>
       <c r="N106" s="6">
         <v>290</v>
@@ -17553,7 +17745,7 @@
       </c>
       <c r="L107" s="4"/>
       <c r="M107" s="5">
-        <v>27701.909999999996</v>
+        <v>25175.610000000004</v>
       </c>
       <c r="N107" s="6">
         <v>299</v>
@@ -17710,7 +17902,7 @@
       </c>
       <c r="L108" s="4"/>
       <c r="M108" s="5">
-        <v>24010.560000000001</v>
+        <v>21522.52</v>
       </c>
       <c r="N108" s="6">
         <v>310</v>
@@ -17867,7 +18059,7 @@
       </c>
       <c r="L109" s="4"/>
       <c r="M109" s="5">
-        <v>26551.799999999999</v>
+        <v>24138.82</v>
       </c>
       <c r="N109" s="6">
         <v>295</v>
@@ -18024,7 +18216,7 @@
       </c>
       <c r="L110" s="4"/>
       <c r="M110" s="5">
-        <v>36613.5</v>
+        <v>33826.790000000001</v>
       </c>
       <c r="N110" s="6">
         <v>345</v>
@@ -18181,7 +18373,7 @@
       </c>
       <c r="L111" s="4"/>
       <c r="M111" s="5">
-        <v>30796.139999999996</v>
+        <v>27455.59</v>
       </c>
       <c r="N111" s="6">
         <v>300</v>
@@ -18338,7 +18530,7 @@
       </c>
       <c r="L112" s="4"/>
       <c r="M112" s="5">
-        <v>64826.240000000005</v>
+        <v>59883.790000000001</v>
       </c>
       <c r="N112" s="6">
         <v>828</v>
@@ -18495,7 +18687,7 @@
       </c>
       <c r="L113" s="4"/>
       <c r="M113" s="5">
-        <v>29380.93</v>
+        <v>27635.790000000001</v>
       </c>
       <c r="N113" s="6">
         <v>321</v>
@@ -18652,7 +18844,7 @@
       </c>
       <c r="L114" s="4"/>
       <c r="M114" s="5">
-        <v>26248.68</v>
+        <v>23872.170000000002</v>
       </c>
       <c r="N114" s="6">
         <v>280</v>
@@ -18809,7 +19001,7 @@
       </c>
       <c r="L115" s="4"/>
       <c r="M115" s="5">
-        <v>26974.02</v>
+        <v>25660.920000000002</v>
       </c>
       <c r="N115" s="6">
         <v>394</v>
@@ -18966,7 +19158,7 @@
       </c>
       <c r="L116" s="4"/>
       <c r="M116" s="5">
-        <v>32162.469999999998</v>
+        <v>27933.639999999996</v>
       </c>
       <c r="N116" s="6">
         <v>297</v>
@@ -19121,7 +19313,7 @@
       </c>
       <c r="L117" s="4"/>
       <c r="M117" s="5">
-        <v>23152.130000000001</v>
+        <v>21206.130000000001</v>
       </c>
       <c r="N117" s="6">
         <v>256</v>
@@ -19276,7 +19468,7 @@
       </c>
       <c r="L118" s="4"/>
       <c r="M118" s="5">
-        <v>107619.88999999998</v>
+        <v>94515.360000000001</v>
       </c>
       <c r="N118" s="6">
         <v>1053</v>
@@ -19433,7 +19625,7 @@
       </c>
       <c r="L119" s="4"/>
       <c r="M119" s="5">
-        <v>64141.280000000013</v>
+        <v>58859.970000000008</v>
       </c>
       <c r="N119" s="6">
         <v>597</v>
@@ -19589,7 +19781,9 @@
         <v>58</v>
       </c>
       <c r="L120" s="4"/>
-      <c r="M120" s="5"/>
+      <c r="M120" s="5">
+        <v>16036.83</v>
+      </c>
       <c r="N120" s="6"/>
       <c r="O120" s="6"/>
       <c r="P120" s="7"/>
@@ -19687,7 +19881,7 @@
       </c>
       <c r="L121" s="4"/>
       <c r="M121" s="5">
-        <v>60870.619999999995</v>
+        <v>53891.870000000003</v>
       </c>
       <c r="N121" s="6">
         <v>608</v>
@@ -19842,7 +20036,7 @@
       </c>
       <c r="L122" s="4"/>
       <c r="M122" s="5">
-        <v>52666.040000000001</v>
+        <v>50180.190000000002</v>
       </c>
       <c r="N122" s="6">
         <v>633</v>
@@ -19999,7 +20193,7 @@
       </c>
       <c r="L123" s="4"/>
       <c r="M123" s="5">
-        <v>62900.319999999992</v>
+        <v>54512.970000000008</v>
       </c>
       <c r="N123" s="6">
         <v>751</v>
@@ -20156,7 +20350,7 @@
       </c>
       <c r="L124" s="4"/>
       <c r="M124" s="5">
-        <v>23451.670000000002</v>
+        <v>21908.52</v>
       </c>
       <c r="N124" s="6">
         <v>277</v>
@@ -20313,7 +20507,7 @@
       </c>
       <c r="L125" s="4"/>
       <c r="M125" s="5">
-        <v>34145.580000000002</v>
+        <v>32397.23</v>
       </c>
       <c r="N125" s="6">
         <v>409</v>
@@ -20470,7 +20664,7 @@
       </c>
       <c r="L126" s="4"/>
       <c r="M126" s="5">
-        <v>30182.740000000002</v>
+        <v>28549.849999999999</v>
       </c>
       <c r="N126" s="6">
         <v>350</v>
@@ -20627,7 +20821,7 @@
       </c>
       <c r="L127" s="4"/>
       <c r="M127" s="5">
-        <v>53537.510000000002</v>
+        <v>47748.199999999997</v>
       </c>
       <c r="N127" s="6">
         <v>551</v>
@@ -20784,7 +20978,7 @@
       </c>
       <c r="L128" s="4"/>
       <c r="M128" s="5">
-        <v>31426.219999999998</v>
+        <v>29641.119999999999</v>
       </c>
       <c r="N128" s="6">
         <v>371</v>
@@ -20939,7 +21133,7 @@
       </c>
       <c r="L129" s="4"/>
       <c r="M129" s="5">
-        <v>27685.880000000001</v>
+        <v>26188.07</v>
       </c>
       <c r="N129" s="6">
         <v>304</v>
@@ -21096,7 +21290,7 @@
       </c>
       <c r="L130" s="4"/>
       <c r="M130" s="5">
-        <v>31820.730000000003</v>
+        <v>30099.220000000001</v>
       </c>
       <c r="N130" s="6">
         <v>327</v>
@@ -21253,7 +21447,7 @@
       </c>
       <c r="L131" s="4"/>
       <c r="M131" s="5">
-        <v>24897.560000000001</v>
+        <v>23206.920000000002</v>
       </c>
       <c r="N131" s="6">
         <v>278</v>
@@ -21410,7 +21604,7 @@
       </c>
       <c r="L132" s="4"/>
       <c r="M132" s="5">
-        <v>24141.870000000003</v>
+        <v>22835.790000000001</v>
       </c>
       <c r="N132" s="6">
         <v>264</v>
@@ -21567,7 +21761,7 @@
       </c>
       <c r="L133" s="4"/>
       <c r="M133" s="5">
-        <v>72993.479999999996</v>
+        <v>64241.830000000002</v>
       </c>
       <c r="N133" s="6">
         <v>722</v>
@@ -21723,7 +21917,9 @@
         <v>58</v>
       </c>
       <c r="L134" s="4"/>
-      <c r="M134" s="5"/>
+      <c r="M134" s="5">
+        <v>27407.279999999999</v>
+      </c>
       <c r="N134" s="6"/>
       <c r="O134" s="6"/>
       <c r="P134" s="7"/>
@@ -21823,7 +22019,7 @@
       </c>
       <c r="L135" s="4"/>
       <c r="M135" s="5">
-        <v>32418.170000000002</v>
+        <v>30664.34</v>
       </c>
       <c r="N135" s="6">
         <v>337</v>
@@ -21980,7 +22176,7 @@
       </c>
       <c r="L136" s="4"/>
       <c r="M136" s="5">
-        <v>30311</v>
+        <v>28671.170000000002</v>
       </c>
       <c r="N136" s="6">
         <v>320</v>
@@ -22137,7 +22333,7 @@
       </c>
       <c r="L137" s="4"/>
       <c r="M137" s="5">
-        <v>32742.850000000002</v>
+        <v>30971.459999999999</v>
       </c>
       <c r="N137" s="6">
         <v>314</v>
@@ -22294,7 +22490,7 @@
       </c>
       <c r="L138" s="4"/>
       <c r="M138" s="5">
-        <v>56749.770000000004</v>
+        <v>53510.57</v>
       </c>
       <c r="N138" s="6">
         <v>616</v>
@@ -22447,7 +22643,7 @@
       </c>
       <c r="L139" s="4"/>
       <c r="M139" s="5">
-        <v>31261.119999999999</v>
+        <v>29569.880000000001</v>
       </c>
       <c r="N139" s="6">
         <v>310</v>
@@ -22602,7 +22798,7 @@
       </c>
       <c r="L140" s="4"/>
       <c r="M140" s="5">
-        <v>35692.550000000003</v>
+        <v>32380.110000000004</v>
       </c>
       <c r="N140" s="6">
         <v>450</v>
@@ -22759,7 +22955,7 @@
       </c>
       <c r="L141" s="4"/>
       <c r="M141" s="5">
-        <v>37978.809999999998</v>
+        <v>35609.559999999998</v>
       </c>
       <c r="N141" s="6">
         <v>417</v>
@@ -22916,7 +23112,7 @@
       </c>
       <c r="L142" s="4"/>
       <c r="M142" s="5">
-        <v>83859.470000000001</v>
+        <v>75830.660000000003</v>
       </c>
       <c r="N142" s="6">
         <v>859</v>
@@ -23037,7 +23233,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="143" ht="24.75" customHeight="1">
+    <row r="143" ht="13.5" customHeight="1">
       <c r="A143" s="2">
         <v>19876</v>
       </c>
@@ -23073,7 +23269,7 @@
       </c>
       <c r="L143" s="4"/>
       <c r="M143" s="5">
-        <v>45669.399999999987</v>
+        <v>43422.459999999999</v>
       </c>
       <c r="N143" s="6">
         <v>511</v>
@@ -23230,7 +23426,7 @@
       </c>
       <c r="L144" s="4"/>
       <c r="M144" s="5">
-        <v>34431.659999999996</v>
+        <v>31883.810000000001</v>
       </c>
       <c r="N144" s="6">
         <v>346</v>
@@ -23387,7 +23583,7 @@
       </c>
       <c r="L145" s="4"/>
       <c r="M145" s="5">
-        <v>38297.080000000002</v>
+        <v>34690.910000000003</v>
       </c>
       <c r="N145" s="6">
         <v>334</v>
@@ -23544,7 +23740,7 @@
       </c>
       <c r="L146" s="4"/>
       <c r="M146" s="5">
-        <v>80362.87000000001</v>
+        <v>67716.100000000006</v>
       </c>
       <c r="N146" s="6">
         <v>704</v>
@@ -23701,7 +23897,7 @@
       </c>
       <c r="L147" s="4"/>
       <c r="M147" s="5">
-        <v>44767.420000000006</v>
+        <v>40509.059999999998</v>
       </c>
       <c r="N147" s="6">
         <v>458</v>
@@ -23858,7 +24054,7 @@
       </c>
       <c r="L148" s="4"/>
       <c r="M148" s="5">
-        <v>28649</v>
+        <v>26822.029999999999</v>
       </c>
       <c r="N148" s="6">
         <v>314</v>
@@ -24015,7 +24211,7 @@
       </c>
       <c r="L149" s="4"/>
       <c r="M149" s="5">
-        <v>27130.09</v>
+        <v>24669.610000000004</v>
       </c>
       <c r="N149" s="6">
         <v>301</v>
@@ -24172,7 +24368,7 @@
       </c>
       <c r="L150" s="4"/>
       <c r="M150" s="5">
-        <v>33106.799999999996</v>
+        <v>31315.720000000001</v>
       </c>
       <c r="N150" s="6">
         <v>349</v>
@@ -24329,7 +24525,7 @@
       </c>
       <c r="L151" s="4"/>
       <c r="M151" s="5">
-        <v>25352.420000000002</v>
+        <v>23862.709999999999</v>
       </c>
       <c r="N151" s="6">
         <v>274</v>
@@ -24486,7 +24682,7 @@
       </c>
       <c r="L152" s="4"/>
       <c r="M152" s="5">
-        <v>29636.189999999999</v>
+        <v>27910.880000000001</v>
       </c>
       <c r="N152" s="6">
         <v>291</v>
@@ -24643,7 +24839,7 @@
       </c>
       <c r="L153" s="4"/>
       <c r="M153" s="5">
-        <v>26272.07</v>
+        <v>28599.84</v>
       </c>
       <c r="N153" s="6">
         <v>428</v>
@@ -24798,7 +24994,7 @@
       </c>
       <c r="L154" s="4"/>
       <c r="M154" s="5">
-        <v>15389.319999999998</v>
+        <v>14052.690000000001</v>
       </c>
       <c r="N154" s="6">
         <v>184</v>
@@ -24955,7 +25151,7 @@
       </c>
       <c r="L155" s="4"/>
       <c r="M155" s="5">
-        <v>21632.93</v>
+        <v>19773.329999999998</v>
       </c>
       <c r="N155" s="6">
         <v>291</v>
@@ -25112,7 +25308,7 @@
       </c>
       <c r="L156" s="4"/>
       <c r="M156" s="5">
-        <v>34349.529999999999</v>
+        <v>32525.52</v>
       </c>
       <c r="N156" s="6">
         <v>428</v>
@@ -25267,7 +25463,7 @@
       </c>
       <c r="L157" s="4"/>
       <c r="M157" s="5">
-        <v>50119.059999999998</v>
+        <v>47402.590000000004</v>
       </c>
       <c r="N157" s="6">
         <v>587</v>
@@ -25422,7 +25618,7 @@
       </c>
       <c r="L158" s="4"/>
       <c r="M158" s="5">
-        <v>12255.425000000001</v>
+        <v>12802.16</v>
       </c>
       <c r="N158" s="6">
         <v>78</v>
@@ -25579,7 +25775,7 @@
       </c>
       <c r="L159" s="4"/>
       <c r="M159" s="5">
-        <v>18156.240000000002</v>
+        <v>16368.49</v>
       </c>
       <c r="N159" s="6">
         <v>219</v>
@@ -25736,7 +25932,7 @@
       </c>
       <c r="L160" s="4"/>
       <c r="M160" s="5">
-        <v>30578.43</v>
+        <v>27855.490000000002</v>
       </c>
       <c r="N160" s="6">
         <v>347</v>
@@ -25893,7 +26089,7 @@
       </c>
       <c r="L161" s="4"/>
       <c r="M161" s="5">
-        <v>35929.57</v>
+        <v>32554.939999999999</v>
       </c>
       <c r="N161" s="6">
         <v>466</v>
@@ -26050,7 +26246,7 @@
       </c>
       <c r="L162" s="4"/>
       <c r="M162" s="5">
-        <v>35337.599999999999</v>
+        <v>32126.400000000001</v>
       </c>
       <c r="N162" s="6">
         <v>406</v>
@@ -26207,7 +26403,7 @@
       </c>
       <c r="L163" s="4"/>
       <c r="M163" s="5">
-        <v>52073.669999999998</v>
+        <v>46604.659999999996</v>
       </c>
       <c r="N163" s="6">
         <v>569</v>
@@ -26363,7 +26559,9 @@
         <v>58</v>
       </c>
       <c r="L164" s="4"/>
-      <c r="M164" s="5"/>
+      <c r="M164" s="5">
+        <v>33575.550000000003</v>
+      </c>
       <c r="N164" s="6"/>
       <c r="O164" s="6"/>
       <c r="P164" s="7"/>
@@ -26463,7 +26661,7 @@
       </c>
       <c r="L165" s="4"/>
       <c r="M165" s="5">
-        <v>16881.859999999997</v>
+        <v>15456.780000000001</v>
       </c>
       <c r="N165" s="6">
         <v>228</v>
@@ -26620,7 +26818,7 @@
       </c>
       <c r="L166" s="4"/>
       <c r="M166" s="5">
-        <v>12048.09</v>
+        <v>11153.370000000001</v>
       </c>
       <c r="N166" s="6">
         <v>160</v>
@@ -26777,7 +26975,7 @@
       </c>
       <c r="L167" s="4"/>
       <c r="M167" s="5">
-        <v>27814.060000000001</v>
+        <v>25223.82</v>
       </c>
       <c r="N167" s="6">
         <v>317</v>
@@ -26934,7 +27132,7 @@
       </c>
       <c r="L168" s="4"/>
       <c r="M168" s="5">
-        <v>34377.979999999996</v>
+        <v>31162.57</v>
       </c>
       <c r="N168" s="6">
         <v>422</v>
@@ -27091,7 +27289,7 @@
       </c>
       <c r="L169" s="4"/>
       <c r="M169" s="5">
-        <v>34695.910000000003</v>
+        <v>30689.380000000001</v>
       </c>
       <c r="N169" s="6">
         <v>388</v>
@@ -27248,7 +27446,7 @@
       </c>
       <c r="L170" s="4"/>
       <c r="M170" s="5">
-        <v>22184.240000000002</v>
+        <v>20230.049999999999</v>
       </c>
       <c r="N170" s="6">
         <v>263</v>
@@ -27405,7 +27603,7 @@
       </c>
       <c r="L171" s="4"/>
       <c r="M171" s="5">
-        <v>18442.689999999999</v>
+        <v>16804.310000000001</v>
       </c>
       <c r="N171" s="6">
         <v>201</v>
@@ -27560,7 +27758,7 @@
       </c>
       <c r="L172" s="4"/>
       <c r="M172" s="5">
-        <v>45405.619999999995</v>
+        <v>40938.93</v>
       </c>
       <c r="N172" s="6">
         <v>518</v>
@@ -27717,7 +27915,7 @@
       </c>
       <c r="L173" s="4"/>
       <c r="M173" s="5">
-        <v>18915.139999999996</v>
+        <v>17329.75</v>
       </c>
       <c r="N173" s="6">
         <v>237</v>
@@ -27874,7 +28072,7 @@
       </c>
       <c r="L174" s="4"/>
       <c r="M174" s="5">
-        <v>45619.729999999996</v>
+        <v>41003.480000000003</v>
       </c>
       <c r="N174" s="6">
         <v>517</v>
@@ -27967,7 +28165,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR174" s="4">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c t="s" r="AS174" s="4">
         <v>60</v>
@@ -28006,10 +28204,10 @@
         <v>51</v>
       </c>
       <c t="s" r="D175" s="4">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="E175" s="4">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="F175" s="4">
         <v>54</v>
@@ -28031,7 +28229,7 @@
       </c>
       <c r="L175" s="4"/>
       <c r="M175" s="5">
-        <v>33944.580000000002</v>
+        <v>31032.07</v>
       </c>
       <c r="N175" s="6">
         <v>418</v>
@@ -28124,7 +28322,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR175" s="4">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="AS175" s="4">
         <v>60</v>
@@ -28188,7 +28386,7 @@
       </c>
       <c r="L176" s="4"/>
       <c r="M176" s="5">
-        <v>67634.199999999997</v>
+        <v>60439.050000000003</v>
       </c>
       <c r="N176" s="6">
         <v>686</v>
@@ -28281,7 +28479,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR176" s="4">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c t="s" r="AS176" s="4">
         <v>60</v>
@@ -28323,7 +28521,7 @@
         <v>96</v>
       </c>
       <c t="s" r="E177" s="4">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="F177" s="4">
         <v>54</v>
@@ -28345,7 +28543,7 @@
       </c>
       <c r="L177" s="4"/>
       <c r="M177" s="5">
-        <v>17631.049999999999</v>
+        <v>16191.299999999999</v>
       </c>
       <c r="N177" s="6">
         <v>254</v>
@@ -28438,7 +28636,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR177" s="4">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="AS177" s="4">
         <v>60</v>
@@ -28480,7 +28678,7 @@
         <v>87</v>
       </c>
       <c t="s" r="E178" s="4">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="F178" s="4">
         <v>54</v>
@@ -28502,7 +28700,7 @@
       </c>
       <c r="L178" s="4"/>
       <c r="M178" s="5">
-        <v>33712.100000000006</v>
+        <v>29550.200000000001</v>
       </c>
       <c r="N178" s="6">
         <v>364</v>
@@ -28595,7 +28793,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR178" s="4">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="AS178" s="4">
         <v>60</v>
@@ -28637,7 +28835,7 @@
         <v>90</v>
       </c>
       <c t="s" r="E179" s="4">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="F179" s="4">
         <v>54</v>
@@ -28659,7 +28857,7 @@
       </c>
       <c r="L179" s="4"/>
       <c r="M179" s="5">
-        <v>15001.980000000001</v>
+        <v>13848.620000000001</v>
       </c>
       <c r="N179" s="6">
         <v>193</v>
@@ -28752,7 +28950,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR179" s="4">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="AS179" s="4">
         <v>60</v>
@@ -28794,7 +28992,7 @@
         <v>75</v>
       </c>
       <c t="s" r="E180" s="4">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="F180" s="4">
         <v>54</v>
@@ -28816,7 +29014,7 @@
       </c>
       <c r="L180" s="4"/>
       <c r="M180" s="5">
-        <v>13295.930000000002</v>
+        <v>12222.680000000002</v>
       </c>
       <c r="N180" s="6">
         <v>170</v>
@@ -28909,7 +29107,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR180" s="4">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="AS180" s="4">
         <v>60</v>
@@ -28951,7 +29149,7 @@
         <v>211</v>
       </c>
       <c t="s" r="E181" s="4">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="F181" s="4">
         <v>54</v>
@@ -28973,7 +29171,7 @@
       </c>
       <c r="L181" s="4"/>
       <c r="M181" s="5">
-        <v>37691.849999999999</v>
+        <v>35535.860000000001</v>
       </c>
       <c r="N181" s="6">
         <v>394</v>
@@ -29066,7 +29264,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR181" s="4">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="AS181" s="4">
         <v>60</v>
@@ -29108,7 +29306,7 @@
         <v>110</v>
       </c>
       <c t="s" r="E182" s="4">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="F182" s="4">
         <v>54</v>
@@ -29130,7 +29328,7 @@
       </c>
       <c r="L182" s="4"/>
       <c r="M182" s="5">
-        <v>18255.450000000001</v>
+        <v>17092.220000000001</v>
       </c>
       <c r="N182" s="6">
         <v>204</v>
@@ -29223,7 +29421,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR182" s="4">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="AS182" s="4">
         <v>60</v>
@@ -29265,7 +29463,7 @@
         <v>87</v>
       </c>
       <c t="s" r="E183" s="4">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="F183" s="4">
         <v>54</v>
@@ -29287,7 +29485,7 @@
       </c>
       <c r="L183" s="4"/>
       <c r="M183" s="5">
-        <v>20894.170000000002</v>
+        <v>19236.220000000001</v>
       </c>
       <c r="N183" s="6">
         <v>230</v>
@@ -29380,7 +29578,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR183" s="4">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="AS183" s="4">
         <v>60</v>
@@ -29422,7 +29620,7 @@
         <v>52</v>
       </c>
       <c t="s" r="E184" s="4">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="F184" s="4">
         <v>54</v>
@@ -29444,7 +29642,7 @@
       </c>
       <c r="L184" s="4"/>
       <c r="M184" s="5">
-        <v>24510.360000000004</v>
+        <v>21823.549999999999</v>
       </c>
       <c r="N184" s="6">
         <v>272</v>
@@ -29579,7 +29777,7 @@
         <v>87</v>
       </c>
       <c t="s" r="E185" s="4">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="F185" s="4">
         <v>54</v>
@@ -29601,7 +29799,7 @@
       </c>
       <c r="L185" s="4"/>
       <c r="M185" s="5">
-        <v>32620.920000000002</v>
+        <v>30223.560000000001</v>
       </c>
       <c r="N185" s="6">
         <v>371</v>
@@ -29694,7 +29892,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR185" s="4">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="AS185" s="4">
         <v>60</v>
@@ -29736,7 +29934,7 @@
         <v>52</v>
       </c>
       <c t="s" r="E186" s="4">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="F186" s="4">
         <v>54</v>
@@ -29757,7 +29955,9 @@
         <v>58</v>
       </c>
       <c r="L186" s="4"/>
-      <c r="M186" s="5"/>
+      <c r="M186" s="5">
+        <v>34573.07</v>
+      </c>
       <c r="N186" s="6"/>
       <c r="O186" s="6"/>
       <c r="P186" s="7"/>
@@ -29793,7 +29993,7 @@
         <v>59</v>
       </c>
       <c t="s" r="AR186" s="4">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c t="s" r="AS186" s="4">
         <v>60</v>
@@ -29835,7 +30035,7 @@
         <v>96</v>
       </c>
       <c t="s" r="E187" s="4">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="F187" s="4">
         <v>54</v>
@@ -29857,7 +30057,7 @@
       </c>
       <c r="L187" s="4"/>
       <c r="M187" s="5">
-        <v>30840.060000000001</v>
+        <v>29171.610000000004</v>
       </c>
       <c r="N187" s="6">
         <v>320</v>
@@ -29992,7 +30192,7 @@
         <v>87</v>
       </c>
       <c t="s" r="E188" s="4">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c t="s" r="F188" s="4">
         <v>54</v>
@@ -30013,7 +30213,9 @@
         <v>58</v>
       </c>
       <c r="L188" s="4"/>
-      <c r="M188" s="5"/>
+      <c r="M188" s="5">
+        <v>19985.549999999999</v>
+      </c>
       <c r="N188" s="6"/>
       <c r="O188" s="6"/>
       <c r="P188" s="7"/>
@@ -30079,10 +30281,10 @@
     </row>
     <row r="189" ht="13.5" customHeight="1">
       <c t="s" r="A189" s="11">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="B189" s="11">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C189" s="12"/>
       <c r="D189" s="12"/>
@@ -30095,91 +30297,91 @@
       <c r="K189" s="12"/>
       <c r="L189" s="12"/>
       <c t="s" r="M189" s="11">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="N189" s="11">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="O189" s="11">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="P189" s="11">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="Q189" s="11">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="R189" s="11">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="S189" s="11">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="T189" s="11">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c t="s" r="U189" s="11">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="V189" s="11">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c t="s" r="W189" s="11">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="X189" s="11">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="Y189" s="11">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="Z189" s="11">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c t="s" r="AA189" s="11">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="AB189" s="11">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c t="s" r="AC189" s="11">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c t="s" r="AD189" s="11">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c t="s" r="AE189" s="11">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="AF189" s="11">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="AG189" s="11">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c t="s" r="AH189" s="11">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c t="s" r="AI189" s="11">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c t="s" r="AJ189" s="11">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="AK189" s="11">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="AL189" s="11">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="AM189" s="11">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="AN189" s="11">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="AO189" s="11">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AP189" s="12"/>
       <c t="s" r="AQ189" s="12">
@@ -30196,10 +30398,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX189" s="11">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c t="s" r="AY189" s="11">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AZ189" s="12"/>
       <c r="BA189" s="12"/>
